--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会</t>
+          <t>中国工业与应用数学学会、高等教育出版社</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -368,12 +368,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-17 13:00</t>
+          <t>2026-08-17 05:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-17 17:00</t>
+          <t>2026-08-17 09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -425,12 +425,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-19 12:00</t>
+          <t>2026-08-19 04:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-19 17:00</t>
+          <t>2026-08-19 09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -482,12 +482,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-19 19:00</t>
+          <t>2026-08-19 11:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-19 21:00</t>
+          <t>2026-08-19 13:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-21 19:00</t>
+          <t>2026-08-21 11:00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00</t>
+          <t>2026-08-21 13:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -569,230 +569,230 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="inlineStr" s="2">
         <is>
           <t>在线赛</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="7">
+      <c r="B9" t="inlineStr" s="2">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>牛客练习赛156</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" t="inlineStr" s="3">
+        <is>
+          <t>牛客周赛 Round 158</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="2">
         <is>
           <t>NowCoder</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr" s="2">
         <is>
           <t>算法竞赛</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-28 19:00</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:30</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="F9" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-23 11:00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-23 13:00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr" s="2">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="I9" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr" s="2">
         <is>
           <t>牛客竞赛</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
+      <c r="K9" t="inlineStr" s="2">
+        <is>
+          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>牛客练习赛156</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-28 11:00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28 13:30</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>上海海事大学</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
+      <c r="A11" t="inlineStr" s="2">
+        <is>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="2">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="3">
+        <is>
+          <t>牛客周赛 Round 159</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="2">
+        <is>
+          <t>NowCoder</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="2">
+        <is>
+          <t>算法竞赛</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-30 11:00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-30 13:00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr" s="2">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr" s="2">
+        <is>
+          <t>牛客竞赛</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr" s="2">
+        <is>
+          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026年第七届全国大学生职业发展大赛</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>中国商业经济学会教育培训分会</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23876-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
@@ -809,27 +809,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>上海海事大学</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -839,74 +839,74 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>2026年第七届全国大学生职业发展大赛</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>中国商业经济学会教育培训分会</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t/>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://www.52jingsai.com/article-23876-1.html</t>
         </is>
       </c>
     </row>
@@ -923,27 +923,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -953,17 +953,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
@@ -980,27 +980,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>中国科学技术大学认知智能全国重点实验室</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -1037,22 +1037,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1077,14 +1077,14 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="5">
@@ -1094,54 +1094,54 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t>中国科学技术大学认知智能全国重点实验室</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>挑战赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="5">
@@ -1151,54 +1151,54 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>第十三届中国青年创青春大赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>共青团中央等</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23888-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="5">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t/>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>智能体、本地生活</t>
+          <t>挑战赛</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="5">
@@ -1265,47 +1265,47 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>第十三届中国青年创青春大赛</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t/>
+          <t>共青团中央等</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t/>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t/>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://www.52jingsai.com/article-23888-1.html</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>智能体、本地生活</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t/>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,27 +1389,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -1486,14 +1486,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B25" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1617,27 +1617,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t/>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1959,27 +1959,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2073,27 +2073,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t/>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t/>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t/>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t/>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t/>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t/>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t/>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t/>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>资金流入流出预测-挑战Baseline</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2529,22 +2529,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t/>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2586,27 +2586,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t/>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>资金流入流出预测-挑战Baseline</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2643,27 +2643,27 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t/>
+          <t>金融</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t/>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t/>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2700,27 +2700,27 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t/>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -2747,47 +2747,47 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>工业园区智能化管理</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>包河区人工智能视觉产业港</t>
+          <t/>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t/>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t/>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -2804,47 +2804,47 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t/>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -2861,27 +2861,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>工业园区智能化管理</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>包河区人工智能视觉产业港</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -2968,34 +2968,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B51" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -3032,27 +3032,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -3082,34 +3082,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B53" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -3146,27 +3146,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -3253,34 +3253,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B56" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3367,34 +3367,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B58" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -3481,34 +3481,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B60" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -3545,47 +3545,47 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>创新创业大赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24008-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -3652,54 +3652,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B63" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://www.52jingsai.com/article-24008-1.html</t>
         </is>
       </c>
     </row>
@@ -3709,34 +3709,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B64" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -3766,34 +3766,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B65" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>教学管理与教育服务智能化</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>深圳市云希谷科技有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>硬件设备智能化与场景赋能</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>深圳市康冠科技股份有限公司</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -3880,34 +3880,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B67" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>教学管理与教育服务智能化</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>深圳市云希谷科技有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3917,17 +3917,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>人才培养与求职就业智能化</t>
+          <t>硬件设备智能化与场景赋能</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>深圳市康冠科技股份有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Talent-AI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
         </is>
       </c>
     </row>
@@ -3994,34 +3994,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B69" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>人才培养与求职就业智能化</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4068,17 +4068,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Talent-AI</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>智慧生活助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -5191,14 +5191,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B90" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5265,17 +5265,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>少样本语音合成练手赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -5476,34 +5476,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B95" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -5540,27 +5540,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
@@ -5597,27 +5597,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>跨设备感知与协同执行</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>苏州穿山甲机器人股份有限公司</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5694,14 +5694,14 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=XD-Perception</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="5">
@@ -5711,47 +5711,47 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>金砖国家工商理事会中方理事会等</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23910-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
@@ -5768,27 +5768,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>跨设备感知与协同执行</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>苏州穿山甲机器人股份有限公司</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=XD-Perception</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="5">
@@ -5825,52 +5825,166 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>待核实</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://www.52jingsai.com/article-23910-1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>长光卫星技术股份有限公司</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
           <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>算法</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K101"/>
+  <autoFilter ref="A1:K103"/>
 </worksheet>
 </file>
 
@@ -5897,7 +6011,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-17 15:31</t>
+          <t>2026-08-17 08:02</t>
         </is>
       </c>
     </row>
@@ -5909,7 +6023,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -5921,7 +6035,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会、高等教育出版社</t>
+          <t>中国工业与应用数学学会（高教社杯）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -346,14 +346,14 @@
           <t>在线赛</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B5" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>河南萌新联赛2026第（五）场：信息工程大学</t>
+          <t>2026牛客暑期多校训练营10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -368,17 +368,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-17 05:00</t>
+          <t>2026-08-19 04:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-17 09:00</t>
+          <t>2026-08-19 09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -393,7 +393,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139416?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/133885?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -403,14 +403,14 @@
           <t>在线赛</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B6" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026牛客暑期多校训练营10</t>
+          <t>牛客2026年七夕节比赛</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -425,12 +425,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-19 04:00</t>
+          <t>2026-08-19 11:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-19 09:00</t>
+          <t>2026-08-19 13:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -450,7 +450,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/133885?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139172?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>牛客2026年七夕节比赛</t>
+          <t>牛客小白月赛136</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -482,12 +482,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-19 11:00</t>
+          <t>2026-08-21 11:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-19 13:00</t>
+          <t>2026-08-21 13:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139172?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>牛客小白月赛136</t>
+          <t>牛客周赛 Round 158</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-21 11:00</t>
+          <t>2026-08-23 11:00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-21 13:00</t>
+          <t>2026-08-23 13:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr" s="3">
         <is>
-          <t>牛客周赛 Round 158</t>
+          <t>河南萌新联赛2026第（六）场：郑州大学</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
@@ -596,12 +596,12 @@
       </c>
       <c r="F9" t="inlineStr" s="2">
         <is>
-          <t>2026-08-23 11:00</t>
+          <t>2026-08-24 05:00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr" s="2">
         <is>
-          <t>2026-08-23 13:00</t>
+          <t>2026-08-24 09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr" s="2">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr" s="2">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -683,57 +683,57 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr" s="2">
+      <c r="A11" t="inlineStr">
         <is>
           <t>在线赛</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr" s="2">
+      <c r="B11" t="inlineStr" s="7">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr" s="3">
+      <c r="C11" t="inlineStr">
         <is>
           <t>牛客周赛 Round 159</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr" s="2">
+      <c r="D11" t="inlineStr">
         <is>
           <t>NowCoder</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr" s="2">
+      <c r="E11" t="inlineStr">
         <is>
           <t>算法竞赛</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr" s="2">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-30 11:00</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr" s="2">
+      <c r="G11" t="inlineStr">
         <is>
           <t>2026-08-30 13:00</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr" s="2">
+      <c r="H11" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr" s="2">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>牛客竞赛</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr" s="2">
+      <c r="K11" t="inlineStr">
         <is>
           <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
         </is>
@@ -1255,7 +1255,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="5">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>第十三届中国青年创青春大赛</t>
+          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>共青团中央等</t>
+          <t/>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>智能体、本地生活</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23888-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>智能体、本地生活</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t/>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,27 +1389,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -1429,14 +1429,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B24" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -1486,14 +1486,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B25" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t/>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2016,27 +2016,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t/>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2073,27 +2073,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t/>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t/>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t/>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t/>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t/>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t/>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>资金流入流出预测-挑战Baseline</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2586,27 +2586,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t/>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t/>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>资金流入流出预测-挑战Baseline</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2643,17 +2643,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t/>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2700,27 +2700,27 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t/>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t/>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t/>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -2804,47 +2804,47 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>工业园区智能化管理</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t/>
+          <t>包河区人工智能视觉产业港</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t/>
+          <t>应用</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
         </is>
       </c>
     </row>
@@ -2861,27 +2861,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>工业园区智能化管理</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>包河区人工智能视觉产业港</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -3025,34 +3025,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B52" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -3082,34 +3082,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B53" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3146,27 +3146,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3310,34 +3310,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B57" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -3367,34 +3367,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B58" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -3538,14 +3538,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B61" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -3595,54 +3595,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B62" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://www.52jingsai.com/article-24008-1.html</t>
         </is>
       </c>
     </row>
@@ -3652,54 +3652,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B63" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24008-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -3766,34 +3766,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B65" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>教学管理与教育服务智能化</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>深圳市云希谷科技有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
         </is>
       </c>
     </row>
@@ -3887,12 +3887,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>教学管理与教育服务智能化</t>
+          <t>硬件设备智能化与场景赋能</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>深圳市云希谷科技有限公司</t>
+          <t>深圳市康冠科技股份有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
         </is>
       </c>
     </row>
@@ -3937,34 +3937,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B68" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>硬件设备智能化与场景赋能</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳市康冠科技股份有限公司</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3974,17 +3974,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -3994,34 +3994,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B69" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>人才培养与求职就业智能化</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Talent-AI</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>人才培养与求职就业智能化</t>
+          <t>智慧生活助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4068,17 +4068,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Talent-AI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -5134,14 +5134,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B89" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -5191,14 +5191,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B90" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5265,17 +5265,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -5419,14 +5419,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B94" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -5476,14 +5476,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B95" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
@@ -5540,27 +5540,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>少样本语音合成练手赛</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
@@ -5597,27 +5597,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
@@ -5711,12 +5711,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>跨设备感知与协同执行</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>苏州穿山甲机器人股份有限公司</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5751,14 +5751,14 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=XD-Perception</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="5">
@@ -5768,54 +5768,54 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>跨设备感知与协同执行</t>
+          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>苏州穿山甲机器人股份有限公司</t>
+          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t/>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=XD-Perception</t>
+          <t>https://www.52jingsai.com/article-23910-1.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="5">
@@ -5825,47 +5825,47 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23910-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5922,69 +5922,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>长光卫星技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
           <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K103"/>
+  <autoFilter ref="A1:K102"/>
 </worksheet>
 </file>
 
@@ -6011,7 +5954,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-17 08:02</t>
+          <t>2026-08-17 22:11</t>
         </is>
       </c>
     </row>
@@ -6023,7 +5966,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -6035,7 +5978,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -569,57 +569,57 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr" s="2">
+      <c r="A9" t="inlineStr">
         <is>
           <t>在线赛</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="2">
+      <c r="B9" t="inlineStr" s="7">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr" s="3">
+      <c r="C9" t="inlineStr">
         <is>
           <t>河南萌新联赛2026第（六）场：郑州大学</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr" s="2">
+      <c r="D9" t="inlineStr">
         <is>
           <t>NowCoder</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr" s="2">
+      <c r="E9" t="inlineStr">
         <is>
           <t>算法竞赛</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr" s="2">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-24 05:00</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr" s="2">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-08-24 09:00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr" s="2">
+      <c r="H9" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr" s="2">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>牛客竞赛</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr" s="2">
+      <c r="K9" t="inlineStr">
         <is>
           <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
         </is>
@@ -1139,66 +1139,66 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>智慧交通调度与出行服务</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>交控科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="A19" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="2">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="3">
+        <is>
+          <t>灵巧手与具身智能自主操作</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="2">
+        <is>
+          <t>中国科学院自动化研究所</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="2">
         <is>
           <t>应用</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="F19" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr" s="2">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="inlineStr" s="2">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+      <c r="K19" t="inlineStr" s="2">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="5">
@@ -1208,54 +1208,54 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>挑战赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="5">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t/>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>智能体、本地生活</t>
+          <t>挑战赛</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1300,19 +1300,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="5">
@@ -1322,47 +1322,47 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>第十三届中国青年创青春大赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t/>
+          <t>共青团中央等</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t/>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t/>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://www.52jingsai.com/article-23888-1.html</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>智能体、本地生活</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t/>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
         </is>
       </c>
     </row>
@@ -1429,14 +1429,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B24" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -1543,14 +1543,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B26" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1731,27 +1731,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t/>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1959,17 +1959,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2016,27 +2016,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2073,17 +2073,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2130,27 +2130,27 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t/>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t/>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t/>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t/>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t/>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t/>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t/>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t/>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>资金流入流出预测-挑战Baseline</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2586,22 +2586,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t/>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2643,27 +2643,27 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t/>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>资金流入流出预测-挑战Baseline</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2700,27 +2700,27 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t/>
+          <t>金融</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t/>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t/>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2757,27 +2757,27 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t/>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -2804,47 +2804,47 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>工业园区智能化管理</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>包河区人工智能视觉产业港</t>
+          <t/>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t/>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t/>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -2861,47 +2861,47 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t/>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -2918,27 +2918,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>工业园区智能化管理</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>包河区人工智能视觉产业港</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -3025,34 +3025,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B52" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -3089,27 +3089,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -3139,34 +3139,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B54" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -3310,34 +3310,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B57" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3424,34 +3424,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B59" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -3538,34 +3538,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B61" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -3602,47 +3602,47 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24008-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -3709,54 +3709,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B64" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://www.52jingsai.com/article-24008-1.html</t>
         </is>
       </c>
     </row>
@@ -3766,34 +3766,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B65" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -3823,34 +3823,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B66" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>教学管理与教育服务智能化</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>深圳市云希谷科技有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -3887,12 +3887,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>硬件设备智能化与场景赋能</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>深圳市康冠科技股份有限公司</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -3937,34 +3937,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B68" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>教学管理与教育服务智能化</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>深圳市云希谷科技有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3974,17 +3974,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>人才培养与求职就业智能化</t>
+          <t>硬件设备智能化与场景赋能</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>深圳市康冠科技股份有限公司</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Talent-AI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
         </is>
       </c>
     </row>
@@ -4051,34 +4051,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B70" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>智慧生活助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4943,188 +4943,188 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
+          <t>¥1.23万</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="2">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="3">
+        <is>
+          <t>个性化全周期医疗健康管理</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="2">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="2">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr" s="2">
+        <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J86" t="inlineStr" s="2">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+      <c r="K86" t="inlineStr" s="2">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="2">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="3">
+        <is>
+          <t>居家健康管理与智能监护</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="2">
         <is>
           <t>科大讯飞股份有限公司</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
+      <c r="E87" t="inlineStr" s="2">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr" s="2">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J87" t="inlineStr" s="2">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>多模态语音增强挑战赛</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+      <c r="K87" t="inlineStr" s="2">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="2">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="3">
+        <is>
+          <t>全渠道品牌营销与用户增长</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="2">
         <is>
           <t>科大讯飞股份有限公司</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
+      <c r="E88" t="inlineStr" s="2">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr" s="2">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J88" t="inlineStr" s="2">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+      <c r="K88" t="inlineStr" s="2">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -5134,14 +5134,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B89" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5265,17 +5265,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5322,17 +5322,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -5362,34 +5362,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B93" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -5419,34 +5419,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B94" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -5483,12 +5483,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>少样本语音合成练手赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -5540,27 +5540,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -5597,27 +5597,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -5647,34 +5647,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B98" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -5711,27 +5711,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>跨设备感知与协同执行</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>苏州穿山甲机器人股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5751,14 +5751,14 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=XD-Perception</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="5">
@@ -5768,47 +5768,47 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23910-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
@@ -5825,27 +5825,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -5882,52 +5882,280 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>自适应学习路径决策与伴学</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>¥1.5万</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>待核实</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>https://www.52jingsai.com/article-23910-1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>长光卫星技术股份有限公司</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
           <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>算法</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="2">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="3">
+        <is>
+          <t>智能驾驶与端侧智能</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr" s="2">
+        <is>
+          <t>长城汽车股份有限公司</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr" s="2">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr" s="2">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr" s="2">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr" s="2">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K102"/>
+  <autoFilter ref="A1:K106"/>
 </worksheet>
 </file>
 
@@ -5954,7 +6182,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-17 22:11</t>
+          <t>2026-08-18 16:12</t>
         </is>
       </c>
     </row>
@@ -5966,7 +6194,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -5978,7 +6206,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会（高教社杯）</t>
+          <t>中国工业与应用数学学会、高等教育出版社</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1139,57 +1139,57 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr" s="2">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr" s="3">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr" s="2">
+      <c r="D19" t="inlineStr">
         <is>
           <t>中国科学院自动化研究所</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr" s="2">
+      <c r="E19" t="inlineStr">
         <is>
           <t>应用</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr" s="2">
+      <c r="F19" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr" s="2">
+      <c r="G19" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr" s="2">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr" s="2">
+      <c r="J19" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr" s="2">
+      <c r="K19" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
@@ -1312,7 +1312,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="5">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>第十三届中国青年创青春大赛</t>
+          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>共青团中央等</t>
+          <t/>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>智能体、本地生活</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23888-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,27 +1389,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>智能体、本地生活</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -1486,14 +1486,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B25" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -1543,14 +1543,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B26" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1731,27 +1731,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t/>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1959,17 +1959,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2073,27 +2073,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t/>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2130,27 +2130,27 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t/>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t/>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t/>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t/>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t/>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t/>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t/>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>资金流入流出预测-挑战Baseline</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2643,27 +2643,27 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t/>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t/>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>资金流入流出预测-挑战Baseline</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t/>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2757,27 +2757,27 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t/>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t/>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t/>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -2861,47 +2861,47 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>工业园区智能化管理</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t/>
+          <t>包河区人工智能视觉产业港</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t/>
+          <t>应用</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
         </is>
       </c>
     </row>
@@ -2918,27 +2918,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>工业园区智能化管理</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>包河区人工智能视觉产业港</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -3082,34 +3082,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B53" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -3139,34 +3139,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B54" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3367,34 +3367,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B58" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -3424,34 +3424,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B59" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -3595,14 +3595,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B62" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -3652,54 +3652,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B63" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://www.52jingsai.com/article-24008-1.html</t>
         </is>
       </c>
     </row>
@@ -3709,54 +3709,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B64" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24008-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -3823,34 +3823,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B66" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -3887,12 +3887,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>教学管理与教育服务智能化</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>深圳市云希谷科技有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>教学管理与教育服务智能化</t>
+          <t>硬件设备智能化与场景赋能</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳市云希谷科技有限公司</t>
+          <t>深圳市康冠科技股份有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
         </is>
       </c>
     </row>
@@ -3994,34 +3994,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B69" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>硬件设备智能化与场景赋能</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>深圳市康冠科技股份有限公司</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -4051,34 +4051,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B70" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>智慧生活助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4923,208 +4923,208 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>居家健康管理与智能监护</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>全渠道品牌营销与用户增长</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>算法</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>¥1.23万</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr" s="2">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr" s="3">
-        <is>
-          <t>个性化全周期医疗健康管理</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr" s="2">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr" s="2">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr" s="2">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr" s="2">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr" s="2">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr" s="2">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr" s="2">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr" s="2">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr" s="3">
-        <is>
-          <t>居家健康管理与智能监护</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr" s="2">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr" s="2">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr" s="2">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr" s="2">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr" s="2">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr" s="2">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr" s="2">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr" s="2">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr" s="3">
-        <is>
-          <t>全渠道品牌营销与用户增长</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr" s="2">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr" s="2">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr" s="2">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr" s="2">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr" s="2">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr" s="2">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr" s="2">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -5305,14 +5305,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B92" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -5362,14 +5362,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B93" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -5419,14 +5419,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B94" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -5476,14 +5476,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B95" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -5533,19 +5533,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B96" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -5590,14 +5590,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B97" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
@@ -5711,27 +5711,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>少样本语音合成练手赛</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
@@ -5768,27 +5768,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -5825,12 +5825,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5865,14 +5865,14 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="5">
@@ -5882,54 +5882,54 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t/>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t/>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://www.52jingsai.com/article-23910-1.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="5">
@@ -5939,47 +5939,47 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23910-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -6053,27 +6053,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6093,69 +6093,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr" s="2">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr" s="3">
-        <is>
-          <t>智能驾驶与端侧智能</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr" s="2">
-        <is>
-          <t>长城汽车股份有限公司</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr" s="2">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr" s="2">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr" s="2">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr" s="2">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr" s="2">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr" s="2">
-        <is>
           <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K106"/>
+  <autoFilter ref="A1:K105"/>
 </worksheet>
 </file>
 
@@ -6182,7 +6125,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18 16:12</t>
+          <t>2026-08-18 16:40</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6137,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>104</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6149,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会、高等教育出版社</t>
+          <t>中国工业与应用数学学会（高教社杯）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1312,7 +1312,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="5">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
+          <t>第十三届中国青年创青春大赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t/>
+          <t>共青团中央等</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>智能体、本地生活</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t/>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
+          <t>https://www.52jingsai.com/article-23888-1.html</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,27 +1389,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>智能体、本地生活</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t/>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -1486,14 +1486,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B25" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -1543,14 +1543,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B26" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1731,27 +1731,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1959,17 +1959,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2073,27 +2073,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2130,27 +2130,27 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t/>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t/>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t/>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t/>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t/>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t/>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t/>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>资金流入流出预测-挑战Baseline</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2643,27 +2643,27 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t/>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t/>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>资金流入流出预测-挑战Baseline</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t/>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2757,27 +2757,27 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t/>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -2861,47 +2861,47 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>工业园区智能化管理</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>包河区人工智能视觉产业港</t>
+          <t/>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t/>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t/>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -2918,27 +2918,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>工业园区智能化管理</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>包河区人工智能视觉产业港</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -3082,34 +3082,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B53" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -3139,34 +3139,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B54" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -3367,34 +3367,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B58" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3424,34 +3424,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B59" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -3595,14 +3595,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B62" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -3652,54 +3652,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B63" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24008-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -3709,111 +3709,111 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B64" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://www.52jingsai.com/article-24008-1.html</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>分子性质AI预测练手赛</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>沈阳药科大学</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+      <c r="A65" t="inlineStr" s="2">
+        <is>
+          <t>高校赛事</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="2">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="3">
+        <is>
+          <t>2027年第十届中国大学生工程实践与创新能力大赛</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="2">
+        <is>
+          <t>教育部工程训练教学指导委员会、中国大学生工程实践与创新能力大赛组委会</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr" s="2">
+        <is>
+          <t>待核实</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-24009-1.html</t>
         </is>
       </c>
     </row>
@@ -3823,34 +3823,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B66" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -3880,34 +3880,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B67" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>教学管理与教育服务智能化</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>深圳市云希谷科技有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>硬件设备智能化与场景赋能</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳市康冠科技股份有限公司</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -3994,34 +3994,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B69" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>教学管理与教育服务智能化</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>深圳市云希谷科技有限公司</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
         </is>
       </c>
     </row>
@@ -4058,27 +4058,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>硬件设备智能化与场景赋能</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>深圳市康冠科技股份有限公司</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
         </is>
       </c>
     </row>
@@ -4108,34 +4108,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B71" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4145,17 +4145,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>智慧生活助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4923,17 +4923,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4980,17 +4980,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5094,17 +5094,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5151,17 +5151,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -5305,14 +5305,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B92" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -5476,14 +5476,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B95" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5493,17 +5493,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -5597,12 +5597,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>少样本语音合成练手赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -5704,34 +5704,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B99" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -5761,34 +5761,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B100" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
@@ -5825,27 +5825,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5865,14 +5865,14 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="5">
@@ -5882,47 +5882,47 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23910-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -5939,27 +5939,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5979,14 +5979,14 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="5">
@@ -5996,47 +5996,47 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t/>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+          <t>https://www.52jingsai.com/article-23910-1.html</t>
         </is>
       </c>
     </row>
@@ -6053,52 +6053,166 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>长光卫星技术股份有限公司</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>长光卫星技术股份有限公司</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
           <t>智能驾驶与端侧智能</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>长城汽车股份有限公司</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>应用</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K105"/>
+  <autoFilter ref="A1:K107"/>
 </worksheet>
 </file>
 
@@ -6125,7 +6239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18 16:40</t>
+          <t>2026-08-18 22:09</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6251,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>106</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6263,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -175,19 +175,19 @@
           <t>官方赛事</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B2" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026年高教社杯全国大学生数学建模竞赛</t>
+          <t>2026年第四届“互联网+”技能应用赛</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会（高教社杯）</t>
+          <t>中国技术创业协会技术创新工作委员会</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -202,7 +202,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -222,14 +222,14 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23557-1.html</t>
+          <t>https://www.52jingsai.com/article-23976-1.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>官方赛事</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="6">
@@ -239,32 +239,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026年第四届“互联网+”技能应用赛</t>
+          <t>2026牛客暑期多校训练营10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-19 12:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-08-19 17:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -274,54 +274,54 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23976-1.html</t>
+          <t>https://ac.nowcoder.com/acm/contest/133885?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>官方赛事</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026年中国国际大学生创新大赛</t>
+          <t>牛客2026年七夕节比赛</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部等</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-19 19:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-19 21:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -331,12 +331,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23927-1.html</t>
+          <t>https://ac.nowcoder.com/acm/contest/139172?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -346,14 +346,14 @@
           <t>在线赛</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B5" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026牛客暑期多校训练营10</t>
+          <t>牛客小白月赛136</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -368,12 +368,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-19 04:00</t>
+          <t>2026-08-21 19:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-19 09:00</t>
+          <t>2026-08-21 21:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -393,7 +393,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/133885?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -410,7 +410,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>牛客2026年七夕节比赛</t>
+          <t>牛客周赛 Round 158</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -425,12 +425,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-19 11:00</t>
+          <t>2026-08-23 19:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-19 13:00</t>
+          <t>2026-08-23 21:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -450,7 +450,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139172?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>牛客小白月赛136</t>
+          <t>河南萌新联赛2026第（六）场：郑州大学</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -482,12 +482,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-21 11:00</t>
+          <t>2026-08-24 13:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-21 13:00</t>
+          <t>2026-08-24 17:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 158</t>
+          <t>牛客练习赛156</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-23 11:00</t>
+          <t>2026-08-28 19:00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00</t>
+          <t>2026-08-28 21:30</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>河南萌新联赛2026第（六）场：郑州大学</t>
+          <t>牛客周赛 Round 159</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-24 05:00</t>
+          <t>2026-08-30 19:00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-24 09:00</t>
+          <t>2026-08-30 21:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -621,178 +621,178 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>牛客练习赛156</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-28 11:00</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-28 13:30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 159</t>
+          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>上海海事大学</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-30 11:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-30 13:00</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>2026年第七届全国大学生职业发展大赛</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>中国商业经济学会教育培训分会</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://www.52jingsai.com/article-23876-1.html</t>
         </is>
       </c>
     </row>
@@ -809,27 +809,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>上海海事大学</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -839,74 +839,74 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026年第七届全国大学生职业发展大赛</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>中国商业经济学会教育培训分会</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t/>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23876-1.html</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -923,27 +923,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -953,17 +953,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
@@ -980,27 +980,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>中国科学技术大学认知智能全国重点实验室</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
         </is>
       </c>
     </row>
@@ -1037,27 +1037,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t>中国科学院自动化研究所</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
@@ -1094,27 +1094,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>中国科学技术大学认知智能全国重点实验室</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1134,14 +1134,14 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="5">
@@ -1151,47 +1151,47 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>挑战赛</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -1208,54 +1208,54 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>智能体、本地生活</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t/>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="5">
@@ -1265,54 +1265,54 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t/>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>挑战赛</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t/>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="5">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>第十三届中国青年创青春大赛</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>共青团中央等</t>
+          <t/>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1342,27 +1342,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23888-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -1372,14 +1372,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B23" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>智能体、本地生活</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -1543,14 +1543,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B26" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1617,27 +1617,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t/>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t/>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1731,27 +1731,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1959,27 +1959,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t/>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2073,17 +2073,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t/>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t/>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t/>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t/>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t/>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2244,27 +2244,27 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t/>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t/>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t/>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>资金流入流出预测-挑战Baseline</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2529,27 +2529,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t/>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t/>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2586,27 +2586,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t/>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t/>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>资金流入流出预测-挑战Baseline</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2700,22 +2700,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t/>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t/>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -2747,27 +2747,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>工业园区智能化管理</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t/>
+          <t>包河区人工智能视觉产业港</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2777,17 +2777,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
         </is>
       </c>
     </row>
@@ -2804,47 +2804,47 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -2861,47 +2861,47 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -2918,27 +2918,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>工业园区智能化管理</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>包河区人工智能视觉产业港</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -2968,34 +2968,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B51" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -3032,27 +3032,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3104,12 +3104,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -3139,34 +3139,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B54" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3253,34 +3253,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B56" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -3424,24 +3424,24 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B59" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -3481,34 +3481,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B60" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -3545,47 +3545,47 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>创新创业大赛</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t/>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://www.52jingsai.com/article-24008-1.html</t>
         </is>
       </c>
     </row>
@@ -3595,24 +3595,24 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B62" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -3716,104 +3716,104 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24008-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr" s="2">
-        <is>
-          <t>高校赛事</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr" s="2">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr" s="3">
-        <is>
-          <t>2027年第十届中国大学生工程实践与创新能力大赛</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr" s="2">
-        <is>
-          <t>教育部工程训练教学指导委员会、中国大学生工程实践与创新能力大赛组委会</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr" s="2">
-        <is>
-          <t>待核实</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-24009-1.html</t>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>教学管理与教育服务智能化</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>深圳市云希谷科技有限公司</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
         </is>
       </c>
     </row>
@@ -3823,34 +3823,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B66" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>硬件设备智能化与场景赋能</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>深圳市康冠科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
         </is>
       </c>
     </row>
@@ -3880,34 +3880,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B67" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3917,17 +3917,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -3944,27 +3944,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>智慧生活助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
@@ -4001,27 +4001,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>教学管理与教育服务智能化</t>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>深圳市云希谷科技有限公司</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -4058,27 +4058,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>硬件设备智能化与场景赋能</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>深圳市康冠科技股份有限公司</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -4108,34 +4108,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B71" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4145,17 +4145,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4809,17 +4809,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4923,17 +4923,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5037,17 +5037,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5094,17 +5094,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5151,17 +5151,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -5191,14 +5191,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B90" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -5305,14 +5305,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B92" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5322,17 +5322,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -5362,14 +5362,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B93" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5379,17 +5379,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -5426,27 +5426,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -5476,34 +5476,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B95" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
@@ -5590,34 +5590,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B97" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
@@ -5647,34 +5647,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B98" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -5704,34 +5704,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B99" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
@@ -5761,24 +5761,24 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B100" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>少样本语音合成练手赛</t>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
         </is>
       </c>
     </row>
@@ -5825,12 +5825,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5922,297 +5922,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>自适应学习路径决策与伴学</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>¥1.5万</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>待核实</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>https://www.52jingsai.com/article-23910-1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>长光卫星技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>长光卫星技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>智能驾驶与端侧智能</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>长城汽车股份有限公司</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
           <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K107"/>
+  <autoFilter ref="A1:K102"/>
 </worksheet>
 </file>
 
@@ -6239,7 +5954,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18 22:09</t>
+          <t>2026-08-19 00:40</t>
         </is>
       </c>
     </row>
@@ -6251,7 +5966,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -6263,7 +5978,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -175,19 +175,19 @@
           <t>官方赛事</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B2" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026年第四届“互联网+”技能应用赛</t>
+          <t>2026年高教社杯全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
+          <t>中国工业与应用数学学会</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -202,7 +202,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -212,7 +212,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t/>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -222,7 +222,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23976-1.html</t>
+          <t>https://www.52jingsai.com/article-23557-1.html</t>
         </is>
       </c>
     </row>
@@ -232,14 +232,14 @@
           <t>在线赛</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B3" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026牛客暑期多校训练营10</t>
+          <t>牛客小白月赛136</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -254,12 +254,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-19 12:00</t>
+          <t>2026-08-21 19:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-19 17:00</t>
+          <t>2026-08-21 21:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -279,7 +279,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/133885?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -296,7 +296,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>牛客2026年七夕节比赛</t>
+          <t>牛客周赛 Round 158</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -311,12 +311,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-19 19:00</t>
+          <t>2026-08-23 19:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-19 21:00</t>
+          <t>2026-08-23 21:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -336,7 +336,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139172?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -353,7 +353,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>牛客小白月赛136</t>
+          <t>河南萌新联赛2026第（六）场：郑州大学</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -368,12 +368,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-21 19:00</t>
+          <t>2026-08-24 13:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00</t>
+          <t>2026-08-24 17:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -393,7 +393,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -410,7 +410,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 158</t>
+          <t>牛客练习赛156</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -425,12 +425,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-23 19:00</t>
+          <t>2026-08-28 19:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00</t>
+          <t>2026-08-28 21:30</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -450,7 +450,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>河南萌新联赛2026第（六）场：郑州大学</t>
+          <t>牛客周赛 Round 159</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -482,12 +482,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-24 13:00</t>
+          <t>2026-08-30 19:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-24 17:00</t>
+          <t>2026-08-30 21:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -507,292 +507,292 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>牛客练习赛156</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-28 19:00</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-28 21:30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 159</t>
+          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>上海海事大学</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-30 19:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-30 21:00</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>2026年第七届全国大学生职业发展大赛</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>中国商业经济学会教育培训分会</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://www.52jingsai.com/article-23876-1.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
+          <t>2026年第四届“互联网+”技能应用赛</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>上海海事大学</t>
+          <t>中国技术创业协会技术创新工作委员会</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
+          <t>https://www.52jingsai.com/article-23976-1.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026年第七届全国大学生职业发展大赛</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>中国商业经济学会教育培训分会</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t/>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23876-1.html</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -859,34 +859,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B14" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
@@ -916,9 +916,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B15" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -973,9 +973,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B16" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1087,9 +1087,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B18" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1139,86 +1139,86 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>高校赛事</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>全国高等学校计算机教育研究会</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>挑战赛</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="A19" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="2">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="3">
+        <is>
+          <t>2026年大学生新文科实践创新大赛</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="2">
+        <is>
+          <t>全国新文科教育研究中心</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr" s="2">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr" s="2">
         <is>
           <t>待核实</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="I19" t="inlineStr" s="2">
+        <is>
+          <t>奖项及证书</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr" s="2">
         <is>
           <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+      <c r="K19" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-23999-1.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>高校赛事</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t/>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>智能体、本地生活</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1228,27 +1228,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t/>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,27 +1275,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>医疗健康、自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t/>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>智能体、本地生活</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t/>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
         </is>
       </c>
     </row>
@@ -1372,14 +1372,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B23" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,27 +1389,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -1486,14 +1486,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B25" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1617,27 +1617,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t/>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1959,27 +1959,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2073,27 +2073,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t/>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t/>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t/>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -2227,14 +2227,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B38" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t/>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t/>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -2284,14 +2284,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B39" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t/>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t/>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t/>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -2512,14 +2512,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B43" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>资金流入流出预测-挑战Baseline</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2529,22 +2529,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t/>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2569,14 +2569,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B44" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2586,27 +2586,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t/>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -2626,14 +2626,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B45" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2643,27 +2643,27 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -2683,14 +2683,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B46" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t/>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -2747,47 +2747,47 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>工业园区智能化管理</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>包河区人工智能视觉产业港</t>
+          <t/>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t/>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t/>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ind-park</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -2797,9 +2797,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B48" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2854,9 +2854,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B49" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2911,9 +2911,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B50" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3025,9 +3025,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B52" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3082,9 +3082,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B53" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3139,9 +3139,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B54" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3196,14 +3196,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B55" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -3253,34 +3253,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B56" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3310,34 +3310,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B57" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -3367,19 +3367,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B58" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -3424,19 +3424,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B59" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -3481,14 +3481,14 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B60" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -3538,54 +3538,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B61" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>创新创业大赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24008-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -3595,54 +3595,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B62" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>创新创业支持</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://www.52jingsai.com/article-24008-1.html</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -3709,34 +3709,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B64" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -3766,19 +3766,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B65" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>教学管理与教育服务智能化</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>深圳市云希谷科技有限公司</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -3830,47 +3830,47 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>硬件设备智能化与场景赋能</t>
+          <t>JCIIOT 2026 开发者大赛：工业具身智能挑战赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>深圳市康冠科技股份有限公司</t>
+          <t>清华大学（计算机系）-西门子（中国）有限公司工业智能与物联网联合研究中心</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t/>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>94,000元</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·Biendata数据竞赛</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
+          <t>https://www.biendata.xyz/competition/jciiot/</t>
         </is>
       </c>
     </row>
@@ -5761,9 +5761,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B100" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5818,9 +5818,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B101" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5875,9 +5875,9 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B102" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19 00:40</t>
+          <t>2026-08-19 23:05</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -182,12 +182,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026年高教社杯全国大学生数学建模竞赛</t>
+          <t>2026年中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会</t>
+          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部等</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -202,12 +202,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -222,292 +222,292 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23557-1.html</t>
+          <t>https://www.52jingsai.com/article-23927-1.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>牛客小白月赛136</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-21 19:00</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t/>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 158</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-23 19:00</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>河南萌新联赛2026第（六）场：郑州大学</t>
+          <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>中国科学院自动化研究所</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-24 13:00</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-24 17:00</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>牛客练习赛156</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t/>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-28 19:00</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-28 21:30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t/>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 159</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t/>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-30 19:00</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-30 21:00</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -517,54 +517,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B8" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t/>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -574,81 +574,81 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B9" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>上海海事大学</t>
+          <t/>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026年第七届全国大学生职业发展大赛</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>中国商业经济学会教育培训分会</t>
+          <t/>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -658,84 +658,84 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23876-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026年第四届“互联网+”技能应用赛</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
+          <t/>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t/>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23976-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -752,27 +752,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t/>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t/>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -782,17 +782,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -809,27 +809,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t/>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -859,34 +859,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B14" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>恶劣场景下的车道线检测挑战赛</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>中国矿业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -916,34 +916,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B15" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t/>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -953,17 +953,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -973,34 +973,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B16" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>中国科学技术大学认知智能全国重点实验室</t>
+          <t/>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -1037,47 +1037,47 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t/>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -1087,34 +1087,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B18" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1124,101 +1124,101 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr" s="2">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr" s="3">
-        <is>
-          <t>2026年大学生新文科实践创新大赛</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr" s="2">
-        <is>
-          <t>全国新文科教育研究中心</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr" s="2">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr" s="2">
-        <is>
-          <t>待核实</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr" s="2">
-        <is>
-          <t>奖项及证书</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23999-1.html</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>¥6,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>阿里云天池</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>高校赛事</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t/>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1228,27 +1228,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>医疗健康、自然语言处理、大语言模型</t>
+          <t/>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t/>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Q力星期四·小鹏 AI 出行服务编排 Agent挑战赛</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>智能体、本地生活</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t/>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532505</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,27 +1389,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t/>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t/>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -1436,17 +1436,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t/>
+          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1456,27 +1456,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>创新创业支持及奖项</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://www.52jingsai.com/article-24008-1.html</t>
         </is>
       </c>
     </row>
@@ -1486,54 +1486,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B25" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>智慧生活助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
@@ -1550,47 +1550,47 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -1607,47 +1607,47 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -1664,47 +1664,47 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -1778,27 +1778,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1808,17 +1808,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -1835,27 +1835,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1922,17 +1922,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -1949,27 +1949,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1979,17 +1979,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -2006,27 +2006,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -2063,47 +2063,47 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -2120,27 +2120,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -2177,27 +2177,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2207,17 +2207,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -2227,54 +2227,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B38" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -2284,54 +2284,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B39" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
         </is>
       </c>
     </row>
@@ -2348,47 +2348,47 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t/>
+          <t>应用</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -2462,47 +2462,47 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -2512,54 +2512,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B43" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -2569,54 +2569,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B44" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -2626,34 +2626,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B45" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2663,17 +2663,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -2683,54 +2683,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B46" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -2747,47 +2747,47 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -2797,19 +2797,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B48" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
@@ -2854,34 +2854,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B49" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -2911,34 +2911,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B50" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2958,64 +2958,64 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t/>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t/>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>国际奖项</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://www.52jingsai.com/article-23910-1.html</t>
         </is>
       </c>
     </row>
@@ -3032,27 +3032,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>上海海事大学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3104,12 +3104,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3129,71 +3129,71 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr" s="6">
+      <c r="A54" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="C54" t="inlineStr" s="3">
+        <is>
+          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="2">
+        <is>
+          <t>中国农业大学 - 农业 AI 研究中心</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="2">
         <is>
           <t>算法</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
+      <c r="F54" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr" s="2">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr" s="2">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+      <c r="J54" t="inlineStr" s="2">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr" s="2">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="6">
@@ -3203,27 +3203,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>2026年第四届“互联网+”技能应用赛</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>中国技术创业协会技术创新工作委员会</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t/>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://www.52jingsai.com/article-23976-1.html</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
@@ -3310,34 +3310,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B57" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>中国科学技术大学认知智能全国重点实验室</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
         </is>
       </c>
     </row>
@@ -3431,22 +3431,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="6">
@@ -3488,27 +3488,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3518,17 +3518,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -3538,54 +3538,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B61" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t/>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -3595,24 +3595,24 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B62" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
+          <t/>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3622,27 +3622,27 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>创新创业支持</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24008-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -3652,34 +3652,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B63" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t/>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -3709,54 +3709,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B64" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t/>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t/>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -3773,27 +3773,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -3823,54 +3823,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B66" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JCIIOT 2026 开发者大赛：工业具身智能挑战赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>清华大学（计算机系）-西门子（中国）有限公司工业智能与物联网联合研究中心</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>94,000元</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>AI发现·Biendata数据竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.biendata.xyz/competition/jciiot/</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -3887,27 +3887,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3917,17 +3917,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -3937,34 +3937,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B68" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3994,19 +3994,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B69" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -4051,19 +4051,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B70" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -4108,19 +4108,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B71" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4130,12 +4130,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -4165,19 +4165,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B72" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -4222,19 +4222,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B73" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -4279,19 +4279,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B74" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -4336,19 +4336,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B75" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -4393,34 +4393,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B76" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -4450,34 +4450,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B77" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -4507,19 +4507,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B78" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
         </is>
       </c>
     </row>
@@ -4564,19 +4564,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B79" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -4621,34 +4621,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B80" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4668,292 +4668,292 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>牛客小白月赛136</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-21 11:00</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21 13:00</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>牛客周赛 Round 158</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-23 11:00</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-23 13:00</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t/>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>河南萌新联赛2026第（六）场：郑州大学</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24 05:00</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24 09:00</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>牛客练习赛156</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-28 11:00</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28 13:30</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>牛客周赛 Round 159</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-30 11:00</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30 13:00</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -4963,54 +4963,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B86" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t/>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -5020,54 +5020,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B87" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t/>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -5077,54 +5077,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B88" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t/>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -5134,34 +5134,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B89" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>资金流入流出预测-挑战Baseline</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5171,17 +5171,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
         </is>
       </c>
     </row>
@@ -5198,27 +5198,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -5248,34 +5248,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B91" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -5483,27 +5483,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>少样本语音合成练手赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -5590,34 +5590,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B97" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -5647,34 +5647,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B98" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -5704,34 +5704,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B99" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -5761,24 +5761,24 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B100" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5808,126 +5808,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>长光卫星技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>智能驾驶与端侧智能</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>长城汽车股份有限公司</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K102"/>
+  <autoFilter ref="A1:K100"/>
 </worksheet>
 </file>
 
@@ -5954,7 +5840,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19 23:05</t>
+          <t>2026-08-21 02:45</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5852,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>99</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部等</t>
+          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部、人力资源社会保障部、农业农村部、中国科学院、中国工程院、国家知识产权局、共青团中央、江苏省人民政府等</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -212,7 +212,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>国家级奖项，含金量高</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>创新创业支持及奖项</t>
+          <t>创新创业扶持，国家级赛事</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>国际奖项</t>
+          <t>国际级奖项，金砖国家认可</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3134,57 +3134,57 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr" s="2">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="6">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr" s="3">
+      <c r="C54" t="inlineStr">
         <is>
           <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr" s="2">
+      <c r="D54" t="inlineStr">
         <is>
           <t>中国农业大学 - 农业 AI 研究中心</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr" s="2">
+      <c r="E54" t="inlineStr">
         <is>
           <t>算法</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr" s="2">
+      <c r="F54" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr" s="2">
+      <c r="G54" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr" s="2">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr" s="2">
+      <c r="J54" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr" s="2">
+      <c r="K54" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
         </is>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026年第四届“互联网+”技能应用赛</t>
+          <t>2026年第七届全国大学生职业发展大赛</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
+          <t>中国商业经济学会教育培训分会</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>职业发展相关奖项</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3243,14 +3243,14 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23976-1.html</t>
+          <t>https://www.52jingsai.com/article-23876-1.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="6">
@@ -3260,27 +3260,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>恶劣场景下的车道线检测挑战赛</t>
+          <t>2026年第四届“互联网+”技能应用赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>中国矿业大学</t>
+          <t>中国技术创业协会技术创新工作委员会</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t/>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3290,17 +3290,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>技能证书，协会认可</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+          <t>https://www.52jingsai.com/article-23976-1.html</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中国科学技术大学认知智能全国重点实验室</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
@@ -3431,27 +3431,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t>中国科学技术大学认知智能全国重点实验室</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3471,64 +3471,64 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>高校赛事</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr" s="6">
+      <c r="A60" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>全国高等学校计算机教育研究会</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
+      <c r="C60" t="inlineStr" s="3">
+        <is>
+          <t>2026年第八届大学生语言文字能力大赛（写作/诵读/规范字专项赛）</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="2">
+        <is>
+          <t>中国语文报刊协会读写教学分会</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="2">
         <is>
           <t>比赛</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>奖项及证书</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="F60" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr" s="2">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr" s="2">
+        <is>
+          <t>语言文字能力证书</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr" s="2">
         <is>
           <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+      <c r="K60" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/</t>
         </is>
       </c>
     </row>
@@ -3545,47 +3545,47 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t/>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
@@ -3602,17 +3602,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>2026年大学生新文科实践创新大赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t/>
+          <t>全国新文科教育研究中心</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3622,34 +3622,34 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>新文科创新奖项</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://www.52jingsai.com/article-23999-1.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="6">
@@ -3659,27 +3659,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t/>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t/>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>国家级学会证书，多赛项</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t/>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -3773,47 +3773,47 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t/>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -3830,27 +3830,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -3887,47 +3887,47 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t/>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -3944,27 +3944,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -4058,12 +4058,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -4115,27 +4115,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -4172,12 +4172,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -4400,22 +4400,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -4457,27 +4457,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4554,64 +4554,64 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr" s="6">
+      <c r="A79" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>长光卫星技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+      <c r="C79" t="inlineStr" s="3">
+        <is>
+          <t>2026年世界职业院校技能大赛</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="2">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr" s="2">
+        <is>
+          <t>待核实</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr" s="2">
+        <is>
+          <t>国家级奖项</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-24019-1.html</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>智能驾驶与端侧智能</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>长城汽车股份有限公司</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4668,235 +4668,235 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>牛客小白月赛136</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-21 11:00</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-08-21 13:00</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t/>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 158</t>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-23 11:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>河南萌新联赛2026第（六）场：郑州大学</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-24 05:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-08-24 09:00</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>牛客练习赛156</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-28 11:00</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-08-28 13:30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 159</t>
+          <t>牛客小白月赛136</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-30 11:00</t>
+          <t>2026-08-21 11:00</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-30 13:00</t>
+          <t>2026-08-21 13:00</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
+          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="7">
@@ -4970,54 +4970,54 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>牛客周赛 Round 158</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t/>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-23 11:00</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-23 13:00</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t/>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="7">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>河南萌新联赛2026第（六）场：郑州大学</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t/>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t/>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-24 05:00</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-24 09:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5062,19 +5062,19 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="7">
@@ -5084,32 +5084,32 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>牛客练习赛156</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t/>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t/>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-28 11:00</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-28 13:30</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5119,19 +5119,19 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="7">
@@ -5141,32 +5141,32 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>资金流入流出预测-挑战Baseline</t>
+          <t>牛客周赛 Round 159</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t/>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2026-08-30 11:00</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2026-08-30 13:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
+          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -5198,47 +5198,47 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t/>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t/>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -5255,47 +5255,47 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t/>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t/>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -5312,47 +5312,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t/>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t/>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -5369,27 +5369,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>资金流入流出预测-挑战Baseline</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t/>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -5483,27 +5483,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -5597,12 +5597,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -5711,27 +5711,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -5768,52 +5768,280 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
+          <t>用户新增预测练手赛</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>基于带货视频评论的用户洞察练手赛</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>电力需求预测练手赛</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>科大讯飞xDatawhale</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>多模态RAG图文问答练手赛</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>科大讯飞xDatawhale</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
           <t>少样本语音合成练手赛</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>科大讯飞xDatawhale</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>训练</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>2027-01-31</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
         <is>
           <t>¥0万</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K100"/>
+  <autoFilter ref="A1:K104"/>
 </worksheet>
 </file>
 
@@ -5840,7 +6068,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 02:45</t>
+          <t>2026-08-21 04:34</t>
         </is>
       </c>
     </row>
@@ -5852,7 +6080,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -5864,7 +6092,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -172,7 +172,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>官方赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="5">
@@ -182,27 +182,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026年中国国际大学生创新大赛</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部、人力资源社会保障部、农业农村部、中国科学院、中国工程院、国家知识产权局、共青团中央、江苏省人民政府等</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -212,17 +212,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>国家级奖项，含金量高</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23927-1.html</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
@@ -239,7 +239,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -279,7 +279,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -296,22 +296,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>中国科学院自动化研究所</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -326,17 +326,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
@@ -353,27 +353,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t/>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -383,17 +383,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -410,7 +410,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -420,27 +420,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -450,7 +450,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -477,7 +477,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -648,27 +648,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t/>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -990,27 +990,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1047,27 +1047,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1161,27 +1161,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t/>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t/>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -1379,47 +1379,47 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>智慧生活助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
@@ -1436,27 +1436,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>创新创业扶持，国家级赛事</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24008-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2415,17 +2415,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -2690,12 +2690,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
@@ -2747,27 +2747,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -2804,27 +2804,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
@@ -2854,34 +2854,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B49" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
@@ -2911,34 +2911,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B50" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>上海海事大学</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2958,64 +2958,64 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
+          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
+          <t>中国农业大学 - 农业 AI 研究中心</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>国际级奖项，金砖国家认可</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23910-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>上海海事大学</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3104,12 +3104,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>中国农业大学 - 农业 AI 研究中心</t>
+          <t>中国科学技术大学认知智能全国重点实验室</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3186,14 +3186,14 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="6">
@@ -3203,27 +3203,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026年第七届全国大学生职业发展大赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>中国商业经济学会教育培训分会</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3233,24 +3233,24 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>职业发展相关奖项</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23876-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="6">
@@ -3260,17 +3260,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026年第四届“互联网+”技能应用赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
+          <t/>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3280,27 +3280,27 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>技能证书，协会认可</t>
+          <t/>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23976-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -3317,47 +3317,47 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>恶劣场景下的车道线检测挑战赛</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>中国矿业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t/>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -3374,27 +3374,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t/>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3404,17 +3404,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -3431,104 +3431,104 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>中国科学技术大学认知智能全国重点实验室</t>
+          <t/>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2027-05-25</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>¥11,000</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>阿里云天池</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>野生东北虎个体识别挑战赛</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>北京林业大学</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>算法</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr" s="2">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr" s="3">
-        <is>
-          <t>2026年第八届大学生语言文字能力大赛（写作/诵读/规范字专项赛）</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr" s="2">
-        <is>
-          <t>中国语文报刊协会读写教学分会</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr" s="2">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr" s="2">
-        <is>
-          <t>语言文字能力证书</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/</t>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -3545,27 +3545,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -3602,27 +3602,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026年大学生新文科实践创新大赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>全国新文科教育研究中心</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3632,24 +3632,24 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>新文科创新奖项</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23999-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="6">
@@ -3659,27 +3659,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>国家级学会证书，多赛项</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3716,47 +3716,47 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t/>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -3773,47 +3773,47 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t/>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -3830,27 +3830,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t/>
+          <t>声网</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -3887,47 +3887,47 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t/>
+          <t>声网</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -4058,12 +4058,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -4172,27 +4172,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4202,17 +4202,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -4343,27 +4343,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4383,292 +4383,292 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>牛客小白月赛136</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-21 11:00</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-21 13:00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>牛客周赛 Round 158</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-23 11:00</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-23 13:00</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>河南萌新联赛2026第（六）场：郑州大学</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-24 05:00</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24 09:00</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr" s="2">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr" s="3">
-        <is>
-          <t>2026年世界职业院校技能大赛</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr" s="2">
-        <is>
-          <t>教育部</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr" s="2">
-        <is>
-          <t>待核实</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr" s="2">
-        <is>
-          <t>国家级奖项</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-24019-1.html</t>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>牛客练习赛156</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NowCoder</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>算法竞赛</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-08-28 13:30</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>牛客竞赛</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>在线赛</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>牛客周赛 Round 159</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-30 11:00</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-30 13:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -4678,29 +4678,29 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B81" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t/>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -4735,54 +4735,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B82" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -4792,54 +4792,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B83" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -4849,34 +4849,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B84" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>智能驾驶与端侧智能</t>
+          <t>资金流入流出预测-挑战Baseline</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>长城汽车股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4886,24 +4886,24 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>在线赛</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="7">
@@ -4913,54 +4913,54 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>牛客小白月赛136</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-21 11:00</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-21 13:00</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>在线赛</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="7">
@@ -4970,54 +4970,54 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 158</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-23 11:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>在线赛</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="7">
@@ -5027,54 +5027,54 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>河南萌新联赛2026第（六）场：郑州大学</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-24 05:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-08-24 09:00</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>在线赛</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="7">
@@ -5084,54 +5084,54 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>牛客练习赛156</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-28 11:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-08-28 13:30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>在线赛</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="7">
@@ -5141,47 +5141,47 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 159</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-30 11:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-08-30 13:00</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -5198,47 +5198,47 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -5255,47 +5255,47 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t/>
+          <t>训练</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -5312,47 +5312,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t/>
+          <t>训练</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -5369,27 +5369,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>资金流入流出预测-挑战Baseline</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -5483,12 +5483,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5523,525 +5523,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>小牛翻译</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>沈阳药科大学</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>分子性质AI预测练手赛</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>沈阳药科大学</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>用户新增预测练手赛</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>电力需求预测练手赛</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>多模态RAG图文问答练手赛</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>少样本语音合成练手赛</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K104"/>
+  <autoFilter ref="A1:K95"/>
 </worksheet>
 </file>
 
@@ -6068,7 +5555,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 04:34</t>
+          <t>2026-08-21 04:37</t>
         </is>
       </c>
     </row>
@@ -6080,7 +5567,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>94</t>
         </is>
       </c>
     </row>
@@ -6092,7 +5579,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -172,7 +172,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>官方赛事</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="5">
@@ -182,27 +182,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>2026年中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部等</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t/>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -212,74 +212,74 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>国家级奖项，含金量高</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://www.52jingsai.com/article-23927-1.html</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr" s="5">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>具有多模态能力的客服智能体设计</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>中国电子学会&amp;睿创微纳</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>智能算法</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>¥145,000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>数据竞赛平台</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+      <c r="C3" t="inlineStr" s="3">
+        <is>
+          <t>2026年第四届“外文奖”大学生英语词汇大赛</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t>中国外文局亚太传播中心</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr" s="2">
+        <is>
+          <t>多校认可加分，高博会参展赛事</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-23427-1.html</t>
         </is>
       </c>
     </row>
@@ -296,22 +296,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -326,17 +326,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
@@ -353,27 +353,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t/>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -383,17 +383,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -410,47 +410,47 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t/>
+          <t>中国科学院自动化研究所</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -477,27 +477,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -648,27 +648,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,27 +705,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t/>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -990,27 +990,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1047,17 +1047,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1161,27 +1161,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1218,27 +1218,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,27 +1275,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t/>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t/>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1379,47 +1379,47 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1436,47 +1436,47 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1493,47 +1493,47 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t/>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -1550,27 +1550,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1580,17 +1580,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>创新创业扶持，国家级赛事</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://www.52jingsai.com/article-24008-1.html</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>智慧生活助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -2690,12 +2690,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -2747,27 +2747,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -2804,27 +2804,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -2854,19 +2854,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B49" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -2911,19 +2911,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B50" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>上海海事大学</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
@@ -2968,34 +2968,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B51" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>中国农业大学 - 农业 AI 研究中心</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -3025,34 +3025,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B52" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>恶劣场景下的车道线检测挑战赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>中国矿业大学</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3072,64 +3072,64 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t/>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>国际级奖项，金砖国家认可</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://www.52jingsai.com/article-23910-1.html</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>中国科学技术大学认知智能全国重点实验室</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t>上海海事大学</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
         </is>
       </c>
     </row>
@@ -3260,54 +3260,54 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t/>
+          <t>中国农业大学 - 农业 AI 研究中心</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="6">
@@ -3317,17 +3317,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>2026年第七届全国大学生职业发展大赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t/>
+          <t>中国商业经济学会教育培训分会</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3337,84 +3337,84 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>学会证书，职业发展相关</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://www.52jingsai.com/article-23876-1.html</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr" s="6">
+      <c r="A58" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>自然语言处理</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2027-05-24</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>¥5,000</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>阿里云天池</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+      <c r="C58" t="inlineStr" s="3">
+        <is>
+          <t>2026年数字交互媒体设计赛</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="2">
+        <is>
+          <t>中国技术创业协会技术创新工作委员会</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr" s="2">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr" s="2">
+        <is>
+          <t>协会证书，设计类奖项</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-24021-1.html</t>
         </is>
       </c>
     </row>
@@ -3431,47 +3431,47 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t/>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>中国科学技术大学认知智能全国重点实验室</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3585,121 +3585,121 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr" s="6">
+      <c r="A62" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>野生大熊猫个体识别挑战赛</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>北京林业大学</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+      <c r="C62" t="inlineStr" s="3">
+        <is>
+          <t>2026年第五届大学生普通话大赛</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="2">
+        <is>
+          <t>中国语文报刊协会读写教学分会</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr" s="2">
+        <is>
+          <t>待核实</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr" s="2">
+        <is>
+          <t>多校学科竞赛目录</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-23889-1.html</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr" s="6">
+      <c r="A63" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>企业风险控制与合规管理</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>厦门供应链数智创新有限公司</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+      <c r="C63" t="inlineStr" s="3">
+        <is>
+          <t>2026年第八届大学生语言文字能力大赛（写作/规范字/诵读专项赛）</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="2">
+        <is>
+          <t>中国语文报刊协会读写教学分会等</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr" s="2">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr" s="2">
+        <is>
+          <t>榜单赛事，多校认可</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/</t>
         </is>
       </c>
     </row>
@@ -3716,27 +3716,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3756,14 +3756,14 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="6">
@@ -3773,27 +3773,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t/>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>国家级学会证书，多赛项</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -3830,47 +3830,47 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t/>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t/>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -3887,47 +3887,47 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t/>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t/>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -3944,27 +3944,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t/>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3974,17 +3974,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -4001,47 +4001,47 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t/>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t/>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -4058,12 +4058,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -4115,27 +4115,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -4172,27 +4172,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4202,17 +4202,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -4229,27 +4229,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -4343,27 +4343,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>智能驾驶与端侧智能</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>长城汽车股份有限公司</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4383,292 +4383,292 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>牛客小白月赛136</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-21 11:00</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-08-21 13:00</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139208?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 158</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-23 11:00</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>河南萌新联赛2026第（六）场：郑州大学</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-24 05:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-08-24 09:00</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>牛客练习赛156</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-28 11:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-08-28 13:30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 159</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-30 11:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-30 13:00</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -4678,54 +4678,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B81" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t/>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -4735,54 +4735,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B82" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t/>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t/>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t/>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -4792,54 +4792,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B83" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t/>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
         </is>
       </c>
     </row>
@@ -4849,34 +4849,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B84" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>资金流入流出预测-挑战Baseline</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t/>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4886,17 +4886,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -4906,34 +4906,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B85" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="7">
@@ -4970,54 +4970,54 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>牛客周赛 Round 158</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-23 11:00</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-23 13:00</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="7">
@@ -5027,54 +5027,54 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>河南萌新联赛2026第（六）场：郑州大学</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-24 05:00</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-24 09:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="7">
@@ -5084,54 +5084,54 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>牛客练习赛156</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-28 11:00</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-28 13:30</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="7">
@@ -5141,47 +5141,47 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>牛客周赛 Round 159</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-30 11:00</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-30 13:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
         </is>
       </c>
     </row>
@@ -5198,47 +5198,47 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t/>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -5255,47 +5255,47 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t/>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -5312,47 +5312,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t/>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -5369,27 +5369,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>资金流入流出预测-挑战Baseline</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t/>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -5483,52 +5483,565 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>脑PET图像分析和疾病预测练手赛</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>安徽大学</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>基于术语词典干预的机器翻译练手赛</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>小牛翻译</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>沈阳药科大学</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>分子性质AI预测练手赛</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>沈阳药科大学</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>用户新增预测练手赛</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>基于带货视频评论的用户洞察练手赛</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>电力需求预测练手赛</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>科大讯飞xDatawhale</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>多模态RAG图文问答练手赛</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>科大讯飞xDatawhale</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
           <t>少样本语音合成练手赛</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>科大讯飞xDatawhale</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>训练</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>2027-01-31</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
         <is>
           <t>¥0万</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K95"/>
+  <autoFilter ref="A1:K104"/>
 </worksheet>
 </file>
 
@@ -5555,7 +6068,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 04:37</t>
+          <t>2026-08-22 04:32</t>
         </is>
       </c>
     </row>
@@ -5567,7 +6080,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -5579,7 +6092,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -170,66 +170,66 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="inlineStr" s="2">
         <is>
           <t>官方赛事</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="5">
+      <c r="B2" t="inlineStr" s="2">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026年中国国际大学生创新大赛</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部等</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr" s="3">
+        <is>
+          <t>2026年高教社杯全国大学生数学建模竞赛</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t>中国工业与应用数学学会</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
         <is>
           <t>比赛</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>国家级奖项，含金量高</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="F2" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="2">
+        <is>
+          <t>国家级奖项</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="2">
         <is>
           <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://www.52jingsai.com/article-23927-1.html</t>
+      <c r="K2" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-23557-1.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t>企业赛</t>
+          <t>官方赛事</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -239,12 +239,12 @@
       </c>
       <c r="C3" t="inlineStr" s="3">
         <is>
-          <t>2026年第四届“外文奖”大学生英语词汇大赛</t>
+          <t>2026年中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t>中国外文局亚太传播中心</t>
+          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部等</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -259,7 +259,7 @@
       </c>
       <c r="G3" t="inlineStr" s="2">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="2">
@@ -269,7 +269,7 @@
       </c>
       <c r="I3" t="inlineStr" s="2">
         <is>
-          <t>多校认可加分，高博会参展赛事</t>
+          <t>国家级奖项，含金量高</t>
         </is>
       </c>
       <c r="J3" t="inlineStr" s="2">
@@ -279,64 +279,64 @@
       </c>
       <c r="K3" t="inlineStr" s="2">
         <is>
-          <t>https://www.52jingsai.com/article-23427-1.html</t>
+          <t>https://www.52jingsai.com/article-23927-1.html</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>中国电子学会&amp;睿创微纳</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>智能算法</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>¥145,000</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>数据竞赛平台</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+      <c r="A4" t="inlineStr" s="2">
+        <is>
+          <t>官方赛事</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="3">
+        <is>
+          <t>2027年第十届中国大学生工程实践与创新能力大赛</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
+          <t>教育部工程训练教学指导委员会、中国大学生工程实践与创新能力大赛组委会</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr" s="2">
+        <is>
+          <t>预计10月启动报名（按往届）</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-24009-1.html</t>
         </is>
       </c>
     </row>
@@ -353,7 +353,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -393,7 +393,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
@@ -410,22 +410,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -440,17 +440,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -467,27 +467,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>中国科学院自动化研究所</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -497,17 +497,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -534,27 +534,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,27 +762,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1161,27 +1161,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1218,17 +1218,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t/>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1550,161 +1550,161 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Q力星期四</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2027-07-31</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>阿里云天池</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="2">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr" s="3">
+        <is>
           <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr" s="2">
         <is>
           <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr" s="2">
         <is>
           <t>比赛</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F27" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr" s="2">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="H27" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr" s="2">
         <is>
           <t>创新创业扶持，国家级赛事</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" t="inlineStr" s="2">
         <is>
           <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K27" t="inlineStr" s="2">
         <is>
           <t>https://www.52jingsai.com/article-24008-1.html</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr" s="5">
+    <row r="28">
+      <c r="A28" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr" s="2">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>¥1.23万</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>¥1.23万</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+      <c r="C28" t="inlineStr" s="3">
+        <is>
+          <t>JCIIOT 2026 开发者大赛：工业具身智能挑战赛</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="2">
+        <is>
+          <t>清华大学（计算机系）-西门子（中国）有限公司工业智能与物联网联合研究中心</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr" s="2">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr" s="2">
+        <is>
+          <t>94,000元</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·Biendata数据竞赛</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr" s="2">
+        <is>
+          <t>https://www.biendata.xyz/competition/jciiot/</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>智慧生活助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2643,17 +2643,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -2918,12 +2918,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -2975,27 +2975,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -3032,27 +3032,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="5">
@@ -3089,47 +3089,47 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>国际级奖项，金砖国家认可</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23910-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -3139,34 +3139,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B54" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3186,64 +3186,64 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>上海海事大学</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
+      <c r="A55" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr" s="2">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="3">
+        <is>
+          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="2">
+        <is>
+          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr" s="2">
+        <is>
+          <t>待核实</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr" s="2">
+        <is>
+          <t>国际级奖项，金砖国家认可</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-23910-1.html</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>中国农业大学 - 农业 AI 研究中心</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3300,406 +3300,406 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>上海海事大学</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>中国农业大学 - 农业 AI 研究中心</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr" s="2">
+        <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr" s="6">
+      <c r="B59" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr" s="3">
         <is>
           <t>2026年第七届全国大学生职业发展大赛</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D59" t="inlineStr" s="2">
         <is>
           <t>中国商业经济学会教育培训分会</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E59" t="inlineStr" s="2">
         <is>
           <t>比赛</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="F59" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr" s="2">
         <is>
           <t>2026-12-20</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
+      <c r="H59" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr" s="2">
         <is>
           <t>学会证书，职业发展相关</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J59" t="inlineStr" s="2">
         <is>
           <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K59" t="inlineStr" s="2">
         <is>
           <t>https://www.52jingsai.com/article-23876-1.html</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr" s="2">
+    <row r="60">
+      <c r="A60" t="inlineStr" s="2">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr" s="2">
+      <c r="B60" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr" s="3">
+      <c r="C60" t="inlineStr" s="3">
         <is>
           <t>2026年数字交互媒体设计赛</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr" s="2">
+      <c r="D60" t="inlineStr" s="2">
         <is>
           <t>中国技术创业协会技术创新工作委员会</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr" s="2">
+      <c r="E60" t="inlineStr" s="2">
         <is>
           <t>比赛</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr" s="2">
+      <c r="F60" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr" s="2">
         <is>
           <t>2026-12-03</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr" s="2">
+      <c r="H60" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr" s="2">
         <is>
           <t>协会证书，设计类奖项</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr" s="2">
+      <c r="J60" t="inlineStr" s="2">
         <is>
           <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr" s="2">
+      <c r="K60" t="inlineStr" s="2">
         <is>
           <t>https://www.52jingsai.com/article-24021-1.html</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr" s="6">
+    <row r="61">
+      <c r="A61" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C61" t="inlineStr" s="3">
+        <is>
+          <t>2026年第四届“互联网+”技能应用赛</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="2">
+        <is>
+          <t>中国技术创业协会技术创新工作委员会</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr" s="2">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr" s="2">
+        <is>
+          <t>技能证书，协会认可</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-23976-1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>中国矿业大学</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>算法</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr" s="6">
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="6">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>算法</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>中国科学技术大学认知智能全国重点实验室</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr" s="2">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr" s="3">
-        <is>
-          <t>2026年第五届大学生普通话大赛</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr" s="2">
-        <is>
-          <t>中国语文报刊协会读写教学分会</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr" s="2">
-        <is>
-          <t>待核实</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr" s="2">
-        <is>
-          <t>多校学科竞赛目录</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23889-1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr" s="2">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr" s="3">
-        <is>
-          <t>2026年第八届大学生语言文字能力大赛（写作/规范字/诵读专项赛）</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr" s="2">
-        <is>
-          <t>中国语文报刊协会读写教学分会等</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr" s="2">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr" s="2">
-        <is>
-          <t>榜单赛事，多校认可</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/</t>
         </is>
       </c>
     </row>
@@ -3716,27 +3716,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t>中国科学技术大学认知智能全国重点实验室</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3756,235 +3756,235 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>智慧交通调度与出行服务</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>交控科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="2">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="3">
+        <is>
+          <t>2026年大学生新文科实践创新大赛</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="2">
+        <is>
+          <t>全国新文科教育研究中心</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr" s="2">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr" s="2">
+        <is>
+          <t>新文科创新奖项</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-23999-1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr" s="2">
+        <is>
           <t>高校赛事</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr" s="6">
+      <c r="B67" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C67" t="inlineStr" s="3">
         <is>
           <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D67" t="inlineStr" s="2">
         <is>
           <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E67" t="inlineStr" s="2">
         <is>
           <t>比赛</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F67" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr" s="2">
         <is>
           <t>2026-11-25</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
+      <c r="H67" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr" s="2">
         <is>
           <t>国家级学会证书，多赛项</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J67" t="inlineStr" s="2">
         <is>
           <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K67" t="inlineStr" s="2">
         <is>
           <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr" s="6">
+    <row r="68">
+      <c r="A68" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2026CCKS系列赛</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>阿里云天池</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2026CCL系列赛</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>学术顶会论文发表</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>¥40,000</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>阿里云天池</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>自然语言处理</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2027-05-24</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>¥5,000</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>阿里云天池</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+      <c r="C68" t="inlineStr" s="3">
+        <is>
+          <t>第十三届中国青年创青春大赛</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="2">
+        <is>
+          <t>共青团中央等</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr" s="2">
+        <is>
+          <t>待核实</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-23888-1.html</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t/>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -4058,47 +4058,47 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t/>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -4115,27 +4115,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4145,17 +4145,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -4172,104 +4172,104 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t/>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr" s="6">
+      <c r="A73" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>企业风险控制与合规管理</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>厦门供应链数智创新有限公司</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+      <c r="C73" t="inlineStr" s="3">
+        <is>
+          <t>第三届“AI宁波”大赛</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr" s="2">
+        <is>
+          <t>待核实</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-24010-1.html</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -4400,12 +4400,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -4457,27 +4457,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -4571,12 +4571,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -4685,27 +4685,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -4742,27 +4742,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4772,17 +4772,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -4856,12 +4856,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4896,292 +4896,292 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr" s="6">
+      <c r="A85" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>智能驾驶与端侧智能</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>长城汽车股份有限公司</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+      <c r="C85" t="inlineStr" s="3">
+        <is>
+          <t>2026年世界职业院校技能大赛</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="2">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr" s="2">
+        <is>
+          <t>待核实</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr" s="2">
+        <is>
+          <t>国家级奖项</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-24019-1.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 158</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-23 11:00</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>河南萌新联赛2026第（六）场：郑州大学</t>
+          <t>教学管理与教育服务智能化</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>深圳市云希谷科技有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-24 05:00</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-08-24 09:00</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>牛客练习赛156</t>
+          <t>硬件设备智能化与场景赋能</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>深圳市康冠科技股份有限公司</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-28 11:00</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-08-28 13:30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>在线赛</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 159</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-30 11:00</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-08-30 13:00</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t/>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -5191,54 +5191,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B90" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t/>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
         </is>
       </c>
     </row>
@@ -5248,54 +5248,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B91" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t/>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -5305,61 +5305,61 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B92" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t/>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t/>
+          <t>应用</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="7">
@@ -5369,32 +5369,32 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>资金流入流出预测-挑战Baseline</t>
+          <t>牛客周赛 Round 158</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t/>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
+          <t>2026-08-23 11:00</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2026-08-23 13:00</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5404,19 +5404,19 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
+          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="7">
@@ -5426,54 +5426,54 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>河南萌新联赛2026第（六）场：郑州大学</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-24 05:00</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-24 09:00</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="7">
@@ -5483,54 +5483,54 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>牛客练习赛156</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-28 11:00</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-28 13:30</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>在线赛</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="7">
@@ -5540,104 +5540,104 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>牛客周赛 Round 159</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>NowCoder</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法竞赛</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-30 11:00</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-30 13:00</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>牛客竞赛</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr" s="7">
+      <c r="A97" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="2">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>沈阳药科大学</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+      <c r="C97" t="inlineStr" s="3">
+        <is>
+          <t>2026年全国大学生科技知识竞赛</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="2">
+        <is>
+          <t>全国大学生科技知识竞赛组委会</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr" s="2">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-23677-1.html</t>
         </is>
       </c>
     </row>
@@ -5654,47 +5654,47 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t/>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -5711,47 +5711,47 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t/>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -5768,47 +5768,47 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t/>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -5825,27 +5825,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>资金流入流出预测-挑战Baseline</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2016-05-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5855,17 +5855,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -5996,52 +5996,508 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>基于术语词典干预的机器翻译练手赛</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>小牛翻译</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>沈阳药科大学</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>分子性质AI预测练手赛</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>沈阳药科大学</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>用户新增预测练手赛</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>基于带货视频评论的用户洞察练手赛</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>电力需求预测练手赛</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>科大讯飞xDatawhale</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>多模态RAG图文问答练手赛</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>科大讯飞xDatawhale</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>少样本语音合成练手赛</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>科大讯飞xDatawhale</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>训练</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>2027-01-31</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
         <is>
           <t>¥0万</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K104"/>
+  <autoFilter ref="A1:K112"/>
 </worksheet>
 </file>
 
@@ -6068,7 +6524,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22 04:32</t>
+          <t>2026-08-22 16:06</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6536,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6548,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -170,173 +170,173 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr" s="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>官方赛事</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="2">
+      <c r="B2" t="inlineStr" s="5">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="3">
-        <is>
-          <t>2026年高教社杯全国大学生数学建模竞赛</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr" s="2">
-        <is>
-          <t>中国工业与应用数学学会</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr" s="2">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026年中国国际大学生创新大赛</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>教育部等</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>比赛</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr" s="2">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr" s="2">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>国家级奖项</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr" s="2">
+      <c r="J2" t="inlineStr">
         <is>
           <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23557-1.html</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://www.52jingsai.com/article-23927-1.html</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr" s="2">
-        <is>
-          <t>官方赛事</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr" s="2">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="5">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr" s="3">
-        <is>
-          <t>2026年中国国际大学生创新大赛</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr" s="2">
-        <is>
-          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部等</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr" s="2">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr" s="2">
-        <is>
-          <t>国家级奖项，含金量高</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23927-1.html</t>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>中国电子学会&amp;睿创微纳</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>智能算法</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>¥145,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>数据竞赛平台</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr" s="2">
-        <is>
-          <t>官方赛事</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="2">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr" s="3">
-        <is>
-          <t>2027年第十届中国大学生工程实践与创新能力大赛</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr" s="2">
-        <is>
-          <t>教育部工程训练教学指导委员会、中国大学生工程实践与创新能力大赛组委会</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr" s="2">
-        <is>
-          <t>预计10月启动报名（按往届）</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-24009-1.html</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>具有多模态能力的客服智能体设计</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>中国电子学会&amp;睿创微纳</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>智能算法</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>¥145,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>数据竞赛平台</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -353,22 +353,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>中国科学院自动化研究所</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -383,17 +383,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
@@ -410,27 +410,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t/>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -440,17 +440,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -467,47 +467,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t/>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -534,27 +534,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,27 +705,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t/>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,27 +762,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t/>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1047,27 +1047,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1104,17 +1104,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1134,64 +1134,64 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr" s="5">
+      <c r="A19" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="2">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>大语言模型、多模态</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>¥7,100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="C19" t="inlineStr" s="3">
+        <is>
+          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="2">
+        <is>
+          <t>自然语言处理、大语言模型</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr" s="2">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr" s="2">
+        <is>
+          <t>¥20,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr" s="2">
         <is>
           <t>阿里云天池</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+      <c r="K19" t="inlineStr" s="2">
+        <is>
+          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1218,17 +1218,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t/>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t/>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -1550,17 +1550,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t/>
+          <t>工业和信息化部网络安全产业发展中心等</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1570,141 +1570,141 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t/>
+          <t>创新创业支持</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://www.52jingsai.com/article-24008-1.html</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr" s="2">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="5">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr" s="3">
-        <is>
-          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr" s="2">
-        <is>
-          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr" s="2">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr" s="2">
-        <is>
-          <t>创新创业扶持，国家级赛事</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-24008-1.html</t>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>智慧生活助理Skill开发挑战赛</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>¥1.23万</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr" s="2">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr" s="5">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr" s="3">
-        <is>
-          <t>JCIIOT 2026 开发者大赛：工业具身智能挑战赛</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr" s="2">
-        <is>
-          <t>清华大学（计算机系）-西门子（中国）有限公司工业智能与物联网联合研究中心</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr" s="2">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr" s="2">
-        <is>
-          <t>94,000元</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·Biendata数据竞赛</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr" s="2">
-        <is>
-          <t>https://www.biendata.xyz/competition/jciiot/</t>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>科大讯飞股份有限公司</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>¥1.23万</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2643,17 +2643,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -2918,12 +2918,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
@@ -2975,27 +2975,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -3032,27 +3032,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="5">
@@ -3089,47 +3089,47 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>金砖国家工商理事会中方理事会等</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t/>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>国际奖项</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://www.52jingsai.com/article-23910-1.html</t>
         </is>
       </c>
     </row>
@@ -3139,34 +3139,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B54" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3186,64 +3186,64 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr" s="2">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr" s="3">
-        <is>
-          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr" s="2">
-        <is>
-          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr" s="2">
-        <is>
-          <t>待核实</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr" s="2">
-        <is>
-          <t>国际级奖项，金砖国家认可</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23910-1.html</t>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>上海海事大学</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>中国农业大学 - 农业 AI 研究中心</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3300,14 +3300,14 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="6">
@@ -3317,27 +3317,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
+          <t>2026年第七届全国大学生职业发展大赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>上海海事大学</t>
+          <t>中国商业经济学会教育培训分会</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3347,24 +3347,24 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
+          <t>https://www.52jingsai.com/article-23876-1.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="6">
@@ -3374,218 +3374,218 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+          <t>2026年数字交互媒体设计赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中国农业大学 - 农业 AI 研究中心</t>
+          <t>中国技术创业协会技术创新工作委员会</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>奖项及证书</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://www.52jingsai.com/article-24021-1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>恶劣场景下的车道线检测挑战赛</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>中国矿业大学</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>算法</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr" s="2">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="6">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr" s="3">
-        <is>
-          <t>2026年第七届全国大学生职业发展大赛</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr" s="2">
-        <is>
-          <t>中国商业经济学会教育培训分会</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr" s="2">
-        <is>
-          <t>2026-12-20</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr" s="2">
-        <is>
-          <t>学会证书，职业发展相关</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23876-1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr" s="2">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="6">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr" s="3">
-        <is>
-          <t>2026年数字交互媒体设计赛</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr" s="2">
-        <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr" s="2">
-        <is>
-          <t>2026-12-03</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr" s="2">
-        <is>
-          <t>协会证书，设计类奖项</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-24021-1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr" s="2">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr" s="3">
-        <is>
-          <t>2026年第四届“互联网+”技能应用赛</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr" s="2">
-        <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr" s="2">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr" s="2">
-        <is>
-          <t>技能证书，协会认可</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23976-1.html</t>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>中国科学技术大学认知智能全国重点实验室</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
         </is>
       </c>
     </row>
@@ -3602,27 +3602,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>恶劣场景下的车道线检测挑战赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>中国矿业大学</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="6">
@@ -3659,27 +3659,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t/>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -3716,47 +3716,47 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>中国科学技术大学认知智能全国重点实验室</t>
+          <t/>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -3773,218 +3773,218 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t/>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
+          <t>¥40,000</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>阿里云天池</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>自然语言处理</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2027-05-24</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>¥5,000</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>阿里云天池</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CCL25-Eval 打榜赛系列赛</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2027-05-25</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>¥11,000</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>阿里云天池</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>野生东北虎个体识别挑战赛</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>北京林业大学</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
           <t>¥1万</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr" s="2">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr" s="3">
-        <is>
-          <t>2026年大学生新文科实践创新大赛</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr" s="2">
-        <is>
-          <t>全国新文科教育研究中心</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr" s="2">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr" s="2">
-        <is>
-          <t>新文科创新奖项</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23999-1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr" s="2">
-        <is>
-          <t>高校赛事</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr" s="2">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr" s="3">
-        <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr" s="2">
-        <is>
-          <t>全国高等学校计算机教育研究会</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr" s="2">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr" s="2">
-        <is>
-          <t>国家级学会证书，多赛项</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr" s="2">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr" s="3">
-        <is>
-          <t>第十三届中国青年创青春大赛</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr" s="2">
-        <is>
-          <t>共青团中央等</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr" s="2">
-        <is>
-          <t>待核实</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23888-1.html</t>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -4001,47 +4001,47 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -4058,47 +4058,47 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -4115,27 +4115,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t/>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4145,17 +4145,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -4172,104 +4172,104 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t/>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr" s="2">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="6">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr" s="3">
-        <is>
-          <t>第三届“AI宁波”大赛</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr" s="2">
-        <is>
-          <t>待核实</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-24010-1.html</t>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>多模态开放词汇关键词检索挑战赛</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -4400,12 +4400,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -4457,22 +4457,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -4571,27 +4571,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -4628,27 +4628,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4658,17 +4658,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -4685,12 +4685,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -4799,27 +4799,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
@@ -4849,111 +4849,111 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B84" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t/>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr" s="2">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr" s="3">
-        <is>
-          <t>2026年世界职业院校技能大赛</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr" s="2">
-        <is>
-          <t>教育部</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr" s="2">
-        <is>
-          <t>待核实</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr" s="2">
-        <is>
-          <t>国家级奖项</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-24019-1.html</t>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>天池新人实战赛</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>阿里云天池</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -4963,54 +4963,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B86" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t/>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t/>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -5020,34 +5020,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B87" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>教学管理与教育服务智能化</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>深圳市云希谷科技有限公司</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EduMS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -5077,34 +5077,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B88" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>硬件设备智能化与场景赋能</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>深圳市康冠科技股份有限公司</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-smart</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -5134,34 +5134,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B89" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5171,17 +5171,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -5191,24 +5191,24 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B90" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -5248,24 +5248,24 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B91" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -5305,34 +5305,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B92" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>智能驾驶与端侧智能</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>长城汽车股份有限公司</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5352,14 +5352,14 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>在线赛</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="7">
@@ -5369,54 +5369,54 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 158</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-23 11:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139659?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>在线赛</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="7">
@@ -5426,54 +5426,54 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>河南萌新联赛2026第（六）场：郑州大学</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-24 05:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-08-24 09:00</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139666?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>在线赛</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="7">
@@ -5483,54 +5483,54 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>牛客练习赛156</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-28 11:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-08-28 13:30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139209?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>在线赛</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="7">
@@ -5540,964 +5540,109 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>牛客周赛 Round 159</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NowCoder</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>算法竞赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-30 11:00</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-08-30 13:00</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>牛客竞赛</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://ac.nowcoder.com/acm/contest/139660?from=acm_calendar</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr" s="2">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="7">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr" s="3">
-        <is>
-          <t>2026年全国大学生科技知识竞赛</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr" s="2">
-        <is>
-          <t>全国大学生科技知识竞赛组委会</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr" s="2">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23677-1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>¥1,000,000</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>阿里云天池</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>天池新人实战赛</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>阿里云天池</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>教学系列赛</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>阿里云天池</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>资金流入流出预测-挑战Baseline</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2016-05-10</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>2027-05-06</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>阿里云天池</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/231573</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>北京科技大学</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>少样本语音合成练手赛</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>科大讯飞xDatawhale</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t>训练</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>2027-01-31</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
         <is>
           <t>¥0万</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>安徽大学</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>小牛翻译</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>沈阳药科大学</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>分子性质AI预测练手赛</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>沈阳药科大学</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>用户新增预测练手赛</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>电力需求预测练手赛</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>多模态RAG图文问答练手赛</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>少样本语音合成练手赛</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K112"/>
+  <autoFilter ref="A1:K97"/>
 </worksheet>
 </file>
 
@@ -6524,7 +5669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22 16:06</t>
+          <t>2026-08-23 04:36</t>
         </is>
       </c>
     </row>
@@ -6536,7 +5681,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -6548,7 +5693,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>教育部等</t>
+          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部等</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,17 +705,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t/>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t/>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,27 +876,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t/>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t/>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1047,27 +1047,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1139,57 +1139,57 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr" s="2">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr" s="2">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="5">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr" s="3">
+      <c r="C19" t="inlineStr">
         <is>
           <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr" s="2">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>自然语言处理、大语言模型</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr" s="2">
+      <c r="F19" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr" s="2">
+      <c r="G19" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr" s="2">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>¥20,000</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr" s="2">
+      <c r="J19" t="inlineStr">
         <is>
           <t>阿里云天池</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr" s="2">
+      <c r="K19" t="inlineStr">
         <is>
           <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
         </is>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>工业和信息化部网络安全产业发展中心等</t>
+          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>金砖国家工商理事会中方理事会等</t>
+          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>国家级学会奖项</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23 04:36</t>
+          <t>2026-08-24 04:44</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -212,7 +212,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>国家级奖项，奖金丰厚</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>创新创业支持</t>
+          <t>创新创业支持，奖金及资源对接</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>国际奖项</t>
+          <t>国际级荣誉，技能认证</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>获奖证书，职业发展指导</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>获奖证书，优秀作品展示</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3590,66 +3590,66 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr" s="6">
+      <c r="A62" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>智慧交通调度与出行服务</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>交控科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+      <c r="C62" t="inlineStr" s="3">
+        <is>
+          <t>2026年第八届大学生语言文字能力大赛</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="2">
+        <is>
+          <t>中国语文报刊协会读写教学分会</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr" s="2">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr" s="2">
+        <is>
+          <t>获奖证书，多校认可</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-23940-1.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="6">
@@ -3659,27 +3659,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3689,24 +3689,24 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>国家级学会奖项</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="6">
@@ -3716,17 +3716,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t/>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3736,27 +3736,27 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t/>
+          <t>获奖证书，部分高校认可</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t/>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3840,27 +3840,27 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t/>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3897,27 +3897,27 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥5,000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
         </is>
       </c>
     </row>
@@ -3944,47 +3944,47 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t/>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -4115,27 +4115,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -4172,27 +4172,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -4400,12 +4400,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -4457,12 +4457,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -4571,27 +4571,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
@@ -4628,27 +4628,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4658,17 +4658,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -4685,27 +4685,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
         </is>
       </c>
     </row>
@@ -4799,27 +4799,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>智能驾驶与端侧智能</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>长城汽车股份有限公司</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -4849,29 +4849,29 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B84" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t/>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4881,22 +4881,22 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -5027,47 +5027,47 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t/>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t/>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t/>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -5141,12 +5141,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -5312,27 +5312,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5379,17 +5379,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -5483,12 +5483,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -5597,52 +5597,109 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>多模态RAG图文问答练手赛</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>科大讯飞xDatawhale</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
           <t>少样本语音合成练手赛</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>科大讯飞xDatawhale</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>训练</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>2027-01-31</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
         <is>
           <t>¥0万</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K97"/>
+  <autoFilter ref="A1:K98"/>
 </worksheet>
 </file>
 
@@ -5669,7 +5726,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 04:44</t>
+          <t>2026-08-25 04:38</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5750,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -182,12 +182,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026年中国国际大学生创新大赛</t>
+          <t>2026年高教社杯全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部等</t>
+          <t>中国工业与应用数学学会等</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -202,7 +202,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -212,7 +212,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>国家级奖项，奖金丰厚</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -222,14 +222,14 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23927-1.html</t>
+          <t>https://www.52jingsai.com/article-23557-1.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>官方赛事</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="5">
@@ -239,27 +239,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>2026年中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>教育部等</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t/>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -269,17 +269,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://www.52jingsai.com/article-23927-1.html</t>
         </is>
       </c>
     </row>
@@ -296,7 +296,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -336,7 +336,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
@@ -353,22 +353,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -383,17 +383,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -410,27 +410,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t/>
+          <t>中国科学院自动化研究所</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -440,17 +440,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -477,27 +477,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,27 +705,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,27 +876,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -933,27 +933,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1104,17 +1104,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
+          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型</t>
+          <t>医疗健康、自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>¥20,000</t>
+          <t/>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1218,17 +1218,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥20,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,27 +1389,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t/>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1550,17 +1550,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>第十一届“创客中国”智能体与具身智能中小企业创新创业大赛</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>工业和信息化部网络安全产业发展中心、广东省工业和信息化厅</t>
+          <t/>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1570,27 +1570,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>创新创业支持，奖金及资源对接</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24008-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1607,47 +1607,47 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t/>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t/>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>智慧生活助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>智能办公协同助理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>全场景内容智能创作Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>多源信息检索与分析Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>数据智能分析与应用Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>面向受限场景的多语言语种识别挑战赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>基于用户注册信息的关键词检测挑战赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>政务公文智能处理Skill开发挑战赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.23万</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2643,17 +2643,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -2918,12 +2918,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -2975,27 +2975,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="5">
@@ -3089,47 +3089,47 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026第十届金砖国家技能发展与技术创新大赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>金砖国家工商理事会中方理事会、一带一路暨金砖国家技能发展国际联盟等</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>国际级荣誉，技能认证</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23910-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>中国农业大学 - 农业 AI 研究中心</t>
+          <t>中国农业大学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3305,59 +3305,59 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" t="inlineStr" s="2">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr" s="6">
+      <c r="B57" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026年第七届全国大学生职业发展大赛</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>中国商业经济学会教育培训分会</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
+      <c r="C57" t="inlineStr" s="3">
+        <is>
+          <t>2026年第十届跨境电商专业能力大赛</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="2">
+        <is>
+          <t>中国对外贸易经济合作企业协会</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="2">
         <is>
           <t>比赛</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2026-12-20</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>获奖证书，职业发展指导</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="F57" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr" s="2">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr" s="2">
+        <is>
+          <t>奖项及证书</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr" s="2">
         <is>
           <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>https://www.52jingsai.com/article-23876-1.html</t>
+      <c r="K57" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-24024-1.html</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>获奖证书，优秀作品展示</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3590,66 +3590,66 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr" s="2">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="6">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr" s="3">
-        <is>
-          <t>2026年第八届大学生语言文字能力大赛</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr" s="2">
-        <is>
-          <t>中国语文报刊协会读写教学分会</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr" s="2">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr" s="2">
-        <is>
-          <t>获奖证书，多校认可</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-23940-1.html</t>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>智慧交通调度与出行服务</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>交控科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="6">
@@ -3659,27 +3659,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t/>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3689,24 +3689,24 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="6">
@@ -3716,17 +3716,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t/>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3736,27 +3736,27 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>获奖证书，部分高校认可</t>
+          <t/>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t/>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t/>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -3887,27 +3887,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>【打榜赛】CCL25-Eval 任务2：第三届汉语框架语义解析评测</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>自然语言处理</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2027-05-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3917,17 +3917,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥5,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532338</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -3944,47 +3944,47 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -4058,27 +4058,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4130,12 +4130,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -4172,27 +4172,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -4400,12 +4400,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -4457,12 +4457,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>多语言推理能力评测挑战赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4472,12 +4472,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4497,14 +4497,14 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="6">
@@ -4514,47 +4514,47 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>2026年世界职业院校技能大赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>教育部</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t/>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://www.52jingsai.com/article-24019-1.html</t>
         </is>
       </c>
     </row>
@@ -4571,27 +4571,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -4628,27 +4628,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4658,17 +4658,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -4685,27 +4685,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>高分辨率遥感影像水体分割挑战赛</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -4799,27 +4799,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
@@ -4849,29 +4849,29 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B84" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>智能驾驶与端侧智能</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>长城汽车股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4881,22 +4881,22 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t/>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t/>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -5027,47 +5027,47 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t/>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t/>
+          <t>训练</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -5141,12 +5141,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -5312,27 +5312,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5379,17 +5379,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -5483,12 +5483,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5637,69 +5637,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>少样本语音合成练手赛</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K98"/>
+  <autoFilter ref="A1:K97"/>
 </worksheet>
 </file>
 
@@ -5726,7 +5669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 04:38</t>
+          <t>2026-08-26 04:39</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5681,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会等</t>
+          <t>中国工业与应用数学学会</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -286,57 +286,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>官方赛事</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>2027年第十届中国大学生工程实践与创新能力大赛</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>教育部工程训练教学指导委员会</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t/>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>预计10月启动报名（按往届）</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://www.52jingsai.com/article-24009-1.html</t>
         </is>
       </c>
     </row>
@@ -353,7 +353,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -393,7 +393,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
@@ -410,22 +410,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -440,17 +440,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -467,27 +467,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>中国科学院自动化研究所</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -497,17 +497,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -534,17 +534,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,27 +762,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -933,27 +933,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -990,27 +990,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>医疗健康、自然语言处理、大语言模型</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t/>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
+          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
+          <t>医疗健康、自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t/>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
+          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型</t>
+          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥20,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥20,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,12 +1389,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t/>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1664,47 +1664,47 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>智慧生活助理Skill开发挑战赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t/>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SLA-Skill</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>人才匹配与发展智能辅助Skill开发挑战赛</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1731,17 +1731,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=TM-DIA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>智能办公协同助理Skill开发挑战赛</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=OCAS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>金融材料智能解析与风险洞察Skill开发挑战赛</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FARI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>医疗健康智能理解与辅助决策Skill开发挑战赛</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HIDS-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>全场景内容智能创作Skill开发挑战赛</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FSCIC-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>代码智能辅助与质量保障Skill开发挑战赛</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CQA-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>电商内容智能生成与用户洞察Skill开发挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ECGI-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>多源信息检索与分析Skill开发挑战赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MSRA-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>教育智能辅助与个性化学习Skill开发挑战赛</t>
+          <t>在线考试防作弊手机识别挑战赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=EAPL-skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
         </is>
       </c>
     </row>
@@ -2234,27 +2234,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>数据智能分析与应用Skill开发挑战赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DIA-App-Skill</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -2291,27 +2291,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>面向智能营销的目标客群拓展（Lookalike）算法挑战赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Lookalike-AC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
@@ -2341,19 +2341,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B40" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>面向受限场景的多语言语种识别挑战赛</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MLLI-RS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
@@ -2398,19 +2398,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B41" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>基于用户注册信息的关键词检测挑战赛</t>
+          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>中国农业大学</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2445,44 +2445,44 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=KDBURI</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>政务公文智能处理Skill开发挑战赛</t>
+          <t>2026年第七届全国大学生职业发展大赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>中国商业经济学会教育培训分会</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,54 +2492,54 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥1.23万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GDS-skill</t>
+          <t>https://www.52jingsai.com/article-23876-1.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>2026年第十届跨境电商专业能力大赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>中国对外贸易经济合作企业协会</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2549,54 +2549,54 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://www.52jingsai.com/article-24024-1.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>2026年数字交互媒体设计赛</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>中国技术创业协会技术创新工作委员会</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2606,17 +2606,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://www.52jingsai.com/article-24021-1.html</t>
         </is>
       </c>
     </row>
@@ -2626,34 +2626,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B45" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
@@ -2683,19 +2683,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B46" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
@@ -2740,34 +2740,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B47" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2787,44 +2787,44 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>高校赛事</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t/>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -2854,54 +2854,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B49" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t/>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2911,54 +2911,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B50" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t/>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -2968,54 +2968,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B51" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t/>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t/>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -3025,34 +3025,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B52" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -3082,34 +3082,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B53" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>基于现场LIBS光谱的煤炭弹筒发热量预测挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>上海海事大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=LIBS-CBCV</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>中国农业大学</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3300,71 +3300,71 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr" s="2">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr" s="2">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="6">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr" s="3">
-        <is>
-          <t>2026年第十届跨境电商专业能力大赛</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr" s="2">
-        <is>
-          <t>中国对外贸易经济合作企业协会</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr" s="2">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr" s="2">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr" s="2">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr" s="2">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr" s="2">
-        <is>
-          <t>奖项及证书</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr" s="2">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr" s="2">
-        <is>
-          <t>https://www.52jingsai.com/article-24024-1.html</t>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>多模态开放词汇关键词检索挑战赛</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>¥1万</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="6">
@@ -3374,27 +3374,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026年数字交互媒体设计赛</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3404,17 +3404,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24021-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>恶劣场景下的车道线检测挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>中国矿业大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>编程竞赛测试用例生成挑战赛 赛季2</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>中国科学技术大学认知智能全国重点实验室</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3585,14 +3585,14 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=CP-TCG</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="6">
@@ -3602,54 +3602,54 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>2026年世界职业院校技能大赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t>教育部</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t/>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://www.52jingsai.com/article-24019-1.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="6">
@@ -3659,27 +3659,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -3716,47 +3716,47 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t/>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t/>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -3773,47 +3773,47 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t/>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -3830,47 +3830,47 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t/>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t/>
+          <t>应用</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
@@ -3880,54 +3880,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B67" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t/>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -3937,54 +3937,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B68" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t/>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -3994,54 +3994,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B69" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t/>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -4051,34 +4051,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B70" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -4108,34 +4108,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B71" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -4165,34 +4165,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B72" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -4222,34 +4222,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B73" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -4279,34 +4279,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B74" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -4336,19 +4336,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B75" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -4393,34 +4393,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B76" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -4450,24 +4450,24 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B77" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>多语言推理能力评测挑战赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4497,64 +4497,64 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Mul1tiNRC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026年世界职业院校技能大赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24019-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -4564,34 +4564,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B79" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -4621,34 +4621,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B80" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4658,991 +4658,22 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>高分辨率遥感影像水体分割挑战赛</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>长光卫星技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-WS</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>长光卫星技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>智能驾驶与端侧智能</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>长城汽车股份有限公司</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>¥1,000,000</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>阿里云天池</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>天池新人实战赛</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>阿里云天池</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>教学系列赛</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>阿里云天池</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>北京科技大学</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>安徽大学</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>小牛翻译</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>沈阳药科大学</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>分子性质AI预测练手赛</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>沈阳药科大学</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>用户新增预测练手赛</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>电力需求预测练手赛</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>多模态RAG图文问答练手赛</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>少样本语音合成练手赛</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K97"/>
+  <autoFilter ref="A1:K80"/>
 </worksheet>
 </file>
 
@@ -5669,7 +4700,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 04:39</t>
+          <t>2026-08-27 15:01</t>
         </is>
       </c>
     </row>
@@ -5681,7 +4712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>79</t>
         </is>
       </c>
     </row>
@@ -5693,7 +4724,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会</t>
+          <t>中国工业与应用数学学会（高教社杯）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -286,57 +286,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>官方赛事</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2027年第十届中国大学生工程实践与创新能力大赛</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>教育部工程训练教学指导委员会</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>预计10月启动报名（按往届）</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24009-1.html</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
@@ -353,7 +353,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -393,7 +393,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -410,22 +410,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>中国科学院自动化研究所</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -440,17 +440,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
@@ -467,47 +467,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t/>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -534,17 +534,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,27 +705,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -933,27 +933,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -990,27 +990,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t/>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>医疗健康、自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t/>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
+          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>医疗健康、自然语言处理、大语言模型</t>
+          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t/>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
+          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
+          <t>自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥20,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥20,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,12 +1389,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t/>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t/>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -1664,47 +1664,47 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>应用</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -2120,27 +2120,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -2177,27 +2177,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>在线考试防作弊手机识别挑战赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、安徽信息工程学院、上海外国语大学贤达经济人文学院、天津仁爱学院</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=proctor-mobile</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
@@ -2227,34 +2227,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B38" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
@@ -2284,34 +2284,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B39" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>中国农业大学</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2331,14 +2331,14 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="6">
@@ -2348,27 +2348,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>2026年第十届跨境电商专业能力大赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>中国对外贸易经济合作企业协会</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t/>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2378,24 +2378,24 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://www.52jingsai.com/article-24024-1.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="6">
@@ -2405,27 +2405,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+          <t>2026年数字交互媒体设计赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>中国农业大学</t>
+          <t>中国技术创业协会技术创新工作委员会</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t/>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2435,24 +2435,24 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
+          <t>https://www.52jingsai.com/article-24022-1.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="6">
@@ -2462,27 +2462,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026年第七届全国大学生职业发展大赛</t>
+          <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>中国商业经济学会教育培训分会</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,24 +2492,24 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23876-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="6">
@@ -2519,27 +2519,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026年第十届跨境电商专业能力大赛</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>中国对外贸易经济合作企业协会</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2549,24 +2549,24 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24024-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="6">
@@ -2576,27 +2576,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026年数字交互媒体设计赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2606,24 +2606,24 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24021-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="6">
@@ -2633,27 +2633,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>恶劣场景下的车道线检测挑战赛</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>中国矿业大学</t>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t/>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2663,17 +2663,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -2690,47 +2690,47 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t/>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t/>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2747,54 +2747,54 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t/>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="6">
@@ -2804,17 +2804,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t/>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t/>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2824,27 +2824,27 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -2861,47 +2861,47 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -2918,47 +2918,47 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -2975,47 +2975,47 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -3032,27 +3032,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3104,12 +3104,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3414,14 +3414,14 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="6">
@@ -3431,47 +3431,47 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>2026年世界职业院校技能大赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>教育部</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t/>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t/>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://www.52jingsai.com/article-24019-1.html</t>
         </is>
       </c>
     </row>
@@ -3488,22 +3488,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -3545,27 +3545,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3575,24 +3575,24 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="6">
@@ -3602,47 +3602,47 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026年世界职业院校技能大赛</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24019-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
@@ -3709,29 +3709,29 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B64" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t/>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3741,22 +3741,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -3766,54 +3766,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B65" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -3823,54 +3823,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B66" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>智能驾驶与端侧智能</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>长城汽车股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t/>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -3887,47 +3887,47 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t/>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -3944,47 +3944,47 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t/>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t/>
+          <t>训练</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -4001,47 +4001,47 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t/>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t/>
+          <t>训练</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -4058,12 +4058,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -4172,27 +4172,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -4343,27 +4343,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -4400,12 +4400,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -4457,12 +4457,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4497,183 +4497,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>电力需求预测练手赛</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>多模态RAG图文问答练手赛</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>少样本语音合成练手赛</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K80"/>
+  <autoFilter ref="A1:K77"/>
 </worksheet>
 </file>
 
@@ -4700,7 +4529,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01</t>
+          <t>2026-08-28 15:56</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4541,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>76</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会（高教社杯）</t>
+          <t>中国工业与应用数学学会</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -286,57 +286,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>官方赛事</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>2027年第十届中国大学生工程实践与创新能力大赛</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>教育部工程训练教学指导委员会</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t/>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>预计10月启动报名（按往届）</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://www.52jingsai.com/article-24009-1.html</t>
         </is>
       </c>
     </row>
@@ -353,7 +353,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -393,7 +393,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
@@ -410,22 +410,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -440,17 +440,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -467,47 +467,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>中国科学院自动化研究所</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026金融智能创新大赛</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,27 +705,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,27 +762,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -819,27 +819,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -933,27 +933,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -990,27 +990,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>医疗健康、自然语言处理、大语言模型</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t/>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
+          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
+          <t>医疗健康、自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t/>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
+          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型</t>
+          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥20,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥20,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,12 +1389,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t/>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t/>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1664,47 +1664,47 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t/>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -2120,27 +2120,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -2227,34 +2227,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B38" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>中国农业大学</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2331,14 +2331,14 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="6">
@@ -2348,27 +2348,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026年第十届跨境电商专业能力大赛</t>
+          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>中国对外贸易经济合作企业协会</t>
+          <t>中国农业大学</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2378,17 +2378,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24024-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026年数字交互媒体设计赛</t>
+          <t>2026年第十届跨境电商专业能力大赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
+          <t>中国对外贸易经济合作企业协会</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>协会奖项</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2445,14 +2445,14 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24022-1.html</t>
+          <t>https://www.52jingsai.com/article-24024-1.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="6">
@@ -2462,27 +2462,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>恶劣场景下的车道线检测挑战赛</t>
+          <t>2026年数字交互媒体设计赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>中国矿业大学</t>
+          <t>中国技术创业协会技术创新工作委员会</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t/>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,17 +2492,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>协会奖项</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+          <t>https://www.52jingsai.com/article-24022-1.html</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
@@ -2576,22 +2576,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2616,14 +2616,14 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="6">
@@ -2633,27 +2633,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2663,24 +2663,24 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="6">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t/>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2710,27 +2710,27 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t/>
+          <t>国家级学会奖项</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t/>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t/>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -2861,47 +2861,47 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t/>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -3032,27 +3032,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -3089,27 +3089,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3414,14 +3414,14 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="6">
@@ -3431,54 +3431,54 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026年世界职业院校技能大赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24019-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="6">
@@ -3488,47 +3488,47 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>2026年世界职业院校技能大赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>教育部</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t/>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://www.52jingsai.com/article-24019-1.html</t>
         </is>
       </c>
     </row>
@@ -3545,27 +3545,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3575,17 +3575,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -3602,27 +3602,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3632,17 +3632,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -3659,27 +3659,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>智能驾驶与端侧智能</t>
+          <t>高分辨率遥感影像土地利用分类挑战赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>长城汽车股份有限公司</t>
+          <t>长光卫星技术股份有限公司</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
         </is>
       </c>
     </row>
@@ -3709,29 +3709,29 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
+      <c r="B64" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t/>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3741,22 +3741,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t/>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -3887,47 +3887,47 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t/>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t/>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t/>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t/>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -4058,12 +4058,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -4172,27 +4172,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>电力需求预测练手赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>科大讯飞xDatawhale</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>多模态RAG图文问答练手赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -4457,52 +4457,109 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>多模态RAG图文问答练手赛</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>科大讯飞xDatawhale</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>¥0万</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>科大讯飞开发者大赛</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
           <t>少样本语音合成练手赛</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>科大讯飞xDatawhale</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>训练</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>2027-01-31</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
         <is>
           <t>¥0万</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>科大讯飞开发者大赛</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K77"/>
+  <autoFilter ref="A1:K78"/>
 </worksheet>
 </file>
 
@@ -4529,7 +4586,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 15:56</t>
+          <t>2026-08-29 11:09</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4598,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -187,7 +187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会</t>
+          <t>中国工业与应用数学学会等</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -286,57 +286,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>官方赛事</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2027年第十届中国大学生工程实践与创新能力大赛</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>教育部工程训练教学指导委员会</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>预计10月启动报名（按往届）</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24009-1.html</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
@@ -353,7 +353,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -393,7 +393,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -410,22 +410,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>灵巧手与具身智能自主操作</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>中国科学院自动化研究所</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -440,17 +440,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
         </is>
       </c>
     </row>
@@ -467,22 +467,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t/>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -492,22 +492,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AFAC2026金融智能创新大赛</t>
+          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/37</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -648,27 +648,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -819,27 +819,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,27 +876,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t/>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -990,27 +990,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t/>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1104,17 +1104,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>医疗健康、自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t/>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
+          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1218,17 +1218,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>医疗健康、自然语言处理、大语言模型</t>
+          <t>自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t/>
+          <t>¥20,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥20,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,27 +1389,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t/>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t/>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -1607,47 +1607,47 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>个性化全周期医疗健康管理</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
         </is>
       </c>
     </row>
@@ -1664,47 +1664,47 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>居家健康管理与智能监护</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>应用</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>全渠道品牌营销与用户增长</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -2063,27 +2063,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -2120,27 +2120,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
@@ -2170,34 +2170,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B37" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
@@ -2227,34 +2227,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B38" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>中国农业大学</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2274,14 +2274,14 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="6">
@@ -2291,27 +2291,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>2026年第十届跨境电商专业能力大赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>中国对外贸易经济合作企业协会</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t/>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2321,24 +2321,24 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://www.52jingsai.com/article-24024-1.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="6">
@@ -2348,27 +2348,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+          <t>2026年数字交互媒体设计赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>中国农业大学</t>
+          <t>中国技术创业协会技术创新工作委员会</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t/>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2378,24 +2378,24 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
+          <t>https://www.52jingsai.com/article-24022-1.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="6">
@@ -2405,27 +2405,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026年第十届跨境电商专业能力大赛</t>
+          <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>中国对外贸易经济合作企业协会</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2435,24 +2435,24 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>协会奖项</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24024-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="6">
@@ -2462,27 +2462,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026年数字交互媒体设计赛</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2492,17 +2492,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>协会奖项</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24022-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
@@ -2519,27 +2519,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>恶劣场景下的车道线检测挑战赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>中国矿业大学</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="6">
@@ -2576,27 +2576,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t/>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2606,17 +2606,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -2633,54 +2633,54 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t/>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="6">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t/>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2710,27 +2710,27 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>国家级学会奖项</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t/>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t/>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -2804,47 +2804,47 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -2861,47 +2861,47 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -2975,27 +2975,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -3089,27 +3089,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3260,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3357,14 +3357,14 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="6">
@@ -3374,47 +3374,47 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>2026年世界职业院校技能大赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t>教育部</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t/>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://www.52jingsai.com/article-24019-1.html</t>
         </is>
       </c>
     </row>
@@ -3431,22 +3431,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="6">
@@ -3488,47 +3488,47 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026年世界职业院校技能大赛</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24019-1.html</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>智能驾驶与端侧智能</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>长城汽车股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
         </is>
       </c>
     </row>
@@ -3595,29 +3595,29 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B62" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t/>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3627,22 +3627,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥1,000,000</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
         </is>
       </c>
     </row>
@@ -3652,54 +3652,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B63" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>高分辨率遥感影像土地利用分类挑战赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>长光卫星技术股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t/>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HRRSI-LUC</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -3709,54 +3709,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B64" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>智能驾驶与端侧智能</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>长城汽车股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t/>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t/>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -3773,47 +3773,47 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t/>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -3830,47 +3830,47 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t/>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t/>
+          <t>训练</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -3887,47 +3887,47 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t/>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t/>
+          <t>训练</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -4058,27 +4058,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>训练</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>¥0万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -4172,12 +4172,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -4229,27 +4229,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>用户新增预测练手赛</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4383,183 +4383,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>电力需求预测练手赛</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>多模态RAG图文问答练手赛</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>少样本语音合成练手赛</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K78"/>
+  <autoFilter ref="A1:K75"/>
 </worksheet>
 </file>
 
@@ -4586,7 +4415,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29 11:09</t>
+          <t>2026-08-30 09:58</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4427,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -286,57 +286,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>官方赛事</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>2027年第十届中国大学生工程实践与创新能力大赛</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t>教育部工程训练教学指导委员会</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t/>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>预计10月启动报名（按往届）</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://www.52jingsai.com/article-24009-1.html</t>
         </is>
       </c>
     </row>
@@ -353,7 +353,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -393,7 +393,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://www.datafountain.cn/competitions/1166</t>
         </is>
       </c>
     </row>
@@ -410,22 +410,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>灵巧手与具身智能自主操作</t>
+          <t>具有多模态能力的客服智能体设计</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>中国科学院自动化研究所</t>
+          <t>中国电子学会&amp;睿创微纳</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -440,17 +440,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥145,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DexNDM</t>
+          <t>https://www.datafountain.cn/competitions/1165</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题三：稀疏反馈下的自动化实验挑战</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -477,12 +477,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532487</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题二：复杂金融文档还原挑战</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、多模态</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532490</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题一：市场参与者交易行为识别与资金流向分析</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,27 +591,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>金融、蚂蚁集团竞赛、大语言模型、智能体</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532489</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t/>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t/>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,27 +876,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>医疗健康、自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t/>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1047,17 +1047,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥20,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1104,17 +1104,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>医疗健康、自然语言处理、大语言模型</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t/>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1218,27 +1218,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>¥20,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1275,27 +1275,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t/>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t/>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t/>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -1436,47 +1436,47 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
         </is>
       </c>
     </row>
@@ -1493,47 +1493,47 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -1550,47 +1550,47 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>个性化全周期医疗健康管理</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1617,17 +1617,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=p4-health-management</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>居家健康管理与智能监护</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1674,17 +1674,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=smart-home-care</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>全渠道品牌营销与用户增长</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=brand-user-growth</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -1778,27 +1778,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
@@ -1828,19 +1828,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B31" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
@@ -1885,19 +1885,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B32" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>中国农业大学</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1932,44 +1932,44 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>2026年第十届跨境电商专业能力大赛</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>中国对外贸易经济合作企业协会</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t/>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1979,54 +1979,54 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://www.52jingsai.com/article-24024-1.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>2026年数字交互媒体设计赛</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>中国技术创业协会技术创新工作委员会</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t/>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://www.52jingsai.com/article-24022-1.html</t>
         </is>
       </c>
     </row>
@@ -2056,34 +2056,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B35" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
@@ -2113,34 +2113,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B36" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
@@ -2177,27 +2177,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>智能量化投资策略建模挑战赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>上海师范大学商学院</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2217,14 +2217,14 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="6">
@@ -2234,27 +2234,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>中国农业大学</t>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t/>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>奖项及证书</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026年第十届跨境电商专业能力大赛</t>
+          <t>第十三届中国青年创青春大赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>中国对外贸易经济合作企业协会</t>
+          <t>共青团中央等</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2311,17 +2311,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t/>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2331,14 +2331,14 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24024-1.html</t>
+          <t>https://www.52jingsai.com/article-23888-1.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="6">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026年数字交互媒体设计赛</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
+          <t/>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2368,27 +2368,27 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t/>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24022-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>恶劣场景下的车道线检测挑战赛</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>中国矿业大学</t>
+          <t/>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t/>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
@@ -2462,47 +2462,47 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t/>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t/>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
@@ -2519,27 +2519,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="6">
@@ -2576,27 +2576,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2606,17 +2606,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -2633,47 +2633,47 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -2690,47 +2690,47 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t/>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -2747,47 +2747,47 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t/>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -2918,12 +2918,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -2975,22 +2975,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="6">
@@ -3089,47 +3089,47 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>2026年世界职业院校技能大赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>教育部</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t/>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>待核实</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>国家级奖项</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://www.52jingsai.com/article-24019-1.html</t>
         </is>
       </c>
     </row>
@@ -3146,27 +3146,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>AI新睿人才“星探计划”</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>烟台睿创微纳技术股份有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>智能算法</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>数据竞赛平台</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://www.datafountain.cn/competitions/1169</t>
         </is>
       </c>
     </row>
@@ -3253,54 +3253,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B56" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t/>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t/>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -3310,111 +3310,111 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B57" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t/>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t/>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026年世界职业院校技能大赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24019-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
@@ -3424,34 +3424,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B59" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -3481,34 +3481,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B60" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3518,17 +3518,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -3538,34 +3538,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B61" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>智能驾驶与端侧智能</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>长城汽车股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=edge-ai-for-driving</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -3602,47 +3602,47 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AFAC2026挑战组-赛题四：金融长文本Agent 的动态记忆压缩与高效问答挑战</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t/>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>金融、智能体、蚂蚁集团竞赛、大语言模型</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>¥1,000,000</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532486</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -3659,47 +3659,47 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -3716,47 +3716,47 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t/>
+          <t>训练</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3773,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -3887,12 +3887,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3984,411 +3984,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>分子性质AI预测练手赛</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>沈阳药科大学</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>用户新增预测练手赛</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>基于带货视频评论的用户洞察练手赛</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>电力需求预测练手赛</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>多模态RAG图文问答练手赛</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>少样本语音合成练手赛</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>科大讯飞xDatawhale</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>¥0万</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
           <t>https://challenge.xfyun.cn/topic/info?type=Train-FewShot-VoiceSynth</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K75"/>
+  <autoFilter ref="A1:K68"/>
 </worksheet>
 </file>
 
@@ -4415,7 +4016,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30 09:58</t>
+          <t>2026-08-31 10:55</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4028,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>67</t>
         </is>
       </c>
     </row>

--- a/data/competitions.xlsx
+++ b/data/competitions.xlsx
@@ -182,12 +182,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026年高教社杯全国大学生数学建模竞赛</t>
+          <t>2026年中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国工业与应用数学学会等</t>
+          <t>教育部、中央统战部、中央网信办、国家发展改革委、工业和信息化部等</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -202,7 +202,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -212,7 +212,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>国家级奖项，含金量高</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -222,121 +222,121 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23557-1.html</t>
+          <t>https://www.52jingsai.com/article-23927-1.html</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>官方赛事</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr" s="5">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026年中国国际大学生创新大赛</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>教育部等</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>比赛</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>国家级奖项</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>AI发现·我爱竞赛网</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://www.52jingsai.com/article-23927-1.html</t>
+      <c r="C3" t="inlineStr" s="3">
+        <is>
+          <t>2026 SMP第十四届全国社会媒体处理大会-大模型图网络决策挑战赛</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t>程序设计、智能体、大语言模型</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr" s="2">
+        <is>
+          <t>¥55,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr" s="2">
+        <is>
+          <t>阿里云天池</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr" s="2">
+        <is>
+          <t>https://tianchi.aliyun.com/competition/entrance/532511</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>官方赛事</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="5">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2027年第十届中国大学生工程实践与创新能力大赛</t>
+          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>教育部工程训练教学指导委员会</t>
+          <t/>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>电商、物流</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>预计10月启动报名（按往届）</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24009-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
         </is>
       </c>
     </row>
@@ -353,27 +353,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>“猎鹰·微波智探”—雷达多目标智能探测与识别挑战</t>
+          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t/>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -383,17 +383,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1166</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
         </is>
       </c>
     </row>
@@ -410,27 +410,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>具有多模态能力的客服智能体设计</t>
+          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>中国电子学会&amp;睿创微纳</t>
+          <t/>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -440,17 +440,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¥145,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1165</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>余震预测技术国际大赛</t>
+          <t>IEEE AICAS 2026 Grand Challenge</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -477,17 +477,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>地质科学、地震学、地球物理学</t>
+          <t>大语言模型、多模态</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥7,100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AI+跨境黑客松巅峰赛——用AI解跨境真命题</t>
+          <t>2026-具身仿真合成挑战赛</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -534,22 +534,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>电商、物流</t>
+          <t/>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532509</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道一：生成式图像增强可控性挑战</t>
+          <t>2026-具身安全应用挑战赛</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -591,17 +591,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t/>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532499</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CSIG图像图形技术挑战赛-赛道二：生成式图像增强轻量模型设计挑战</t>
+          <t>2026-跨本体具身认知极限联合挑战赛</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥100,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532500</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IEEE AICAS 2026 Grand Challenge</t>
+          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,27 +705,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>大语言模型、多模态</t>
+          <t>医疗健康、自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>¥7,100</t>
+          <t/>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/34</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-具身仿真合成挑战赛</t>
+          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t/>
+          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532506</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-具身安全应用挑战赛</t>
+          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t/>
+          <t>自然语言处理、大语言模型</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥20,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532507</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-跨本体具身认知极限联合挑战赛</t>
+          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>计算机视觉、工业制造</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>¥100,000</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532508</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CHIP2026-面向生物医学全文的特定患者表型概念识别任务</t>
+          <t>余震预测技术国际大赛</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -933,27 +933,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>医疗健康、自然语言处理、大语言模型</t>
+          <t>地质科学、地震学、地球物理学</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t/>
+          <t>¥30,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532512</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532460</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第一届跨境电商图像文本翻译大赛</t>
+          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>大语言模型、计算机视觉、学术顶会论文发表、电商</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥6,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532463</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>知乎知学堂大模型挑战赛：大模型复杂表格识别与内容理解</t>
+          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1047,27 +1047,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型</t>
+          <t>医疗健康、第三方竞赛</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>¥20,000</t>
+          <t>¥26,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532510</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>第七届CSIG图像图形技术挑战赛—复杂工业场景异常检测算法挑战赛</t>
+          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>计算机视觉、工业制造</t>
+          <t/>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532482</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CCL2026-Eval 任务：第二届古诗词赏析</t>
+          <t>2026-具身极限挑战赛</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1161,27 +1161,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>¥6,000</t>
+          <t>¥300,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532470</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CSS体视学挑战赛：2026 CBCT金属伪影消除挑战赛</t>
+          <t>Q力星期四</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>医疗健康、第三方竞赛</t>
+          <t/>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>¥26,000</t>
+          <t/>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/532440</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
         </is>
       </c>
     </row>
@@ -1265,47 +1265,47 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>欧莱雅第二届美妆科技黑客松 - 用 AI 造点美</t>
+          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>¥200,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/38</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
         </is>
       </c>
     </row>
@@ -1322,47 +1322,47 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-具身极限挑战赛</t>
+          <t>多模态语音增强挑战赛</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/41</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
         </is>
       </c>
     </row>
@@ -1379,47 +1379,47 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Q力星期四</t>
+          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/39</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>面向说话人转写内容的角色分离挑战赛 赛季2</t>
+          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SpkRole-Cup</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
         </is>
       </c>
     </row>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>面向单人演讲的场景下的语音同传Agent设计挑战赛</t>
+          <t>岗位胜任力多轮问询与评估报告生成</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lecture-simul-agent</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
         </is>
       </c>
     </row>
@@ -1550,27 +1550,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>多模态语音增强挑战赛</t>
+          <t>自适应学习路径决策与伴学</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥1.5万</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=mmse-challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
         </is>
       </c>
     </row>
@@ -1600,19 +1600,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B27" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>从自然语言到可执行工作流的Agent算法挑战赛</t>
+          <t>智能量化投资策略建模挑战赛</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>上海师范大学商学院</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NL2Wf</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
         </is>
       </c>
     </row>
@@ -1657,19 +1657,19 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+      <c r="B28" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>基于星评测 Agent 的养虾 Skills 横评挑战赛</t>
+          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司</t>
+          <t>中国农业大学</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1704,44 +1704,44 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ShrimpAIBench</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>岗位胜任力多轮问询与评估报告生成</t>
+          <t>2026年第七届全国大学生职业发展大赛</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、遵义师范学院、广东理工学院、河北金融学院</t>
+          <t>中国商业经济学会教育培训分会</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t/>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1751,54 +1751,54 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>行业认可，含金量中</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Competency-ARS</t>
+          <t>https://www.52jingsai.com/article-23876-1.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr" s="5">
-        <is>
-          <t>高</t>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr" s="6">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>自适应学习路径决策与伴学</t>
+          <t>2026年第十届跨境电商专业能力大赛</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>科大讯飞股份有限公司、陕西科技大学镐京学院、四川科技职业学院、陕西财经职业技术学院</t>
+          <t>中国对外贸易经济合作企业协会</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t/>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1808,74 +1808,74 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>¥1.5万</t>
+          <t>行业认可，奖项含金量中高</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Adaptive-LPDS</t>
+          <t>https://www.52jingsai.com/article-24024-1.html</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr" s="6">
+      <c r="A31" t="inlineStr" s="2">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr" s="2">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>智能量化投资策略建模挑战赛</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>上海师范大学商学院</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=AI-QIM</t>
+      <c r="C31" t="inlineStr" s="3">
+        <is>
+          <t>2026年全国大学生数字交互媒体设计赛</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="2">
+        <is>
+          <t>中国技术创业协会技术创新工作委员会</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr" s="2">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr" s="2">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr" s="2">
+        <is>
+          <t>报名中</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr" s="2">
+        <is>
+          <t>行业奖项，含金量中</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr" s="2">
+        <is>
+          <t>AI发现·我爱竞赛网</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr" s="2">
+        <is>
+          <t>https://www.52jingsai.com/article-24022-1.html</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>复杂田间环境下妮娜皇后葡萄果粒实例分割挑战赛</t>
+          <t>恶劣场景下的车道线检测挑战赛</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>中国农业大学</t>
+          <t>中国矿业大学</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1932,14 +1932,14 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=NinaBerrySeg</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="6">
@@ -1949,27 +1949,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026年第十届跨境电商专业能力大赛</t>
+          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>中国对外贸易经济合作企业协会</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1979,24 +1979,24 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24024-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="6">
@@ -2006,27 +2006,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026年数字交互媒体设计赛</t>
+          <t>智慧交通调度与出行服务</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>中国技术创业协会技术创新工作委员会</t>
+          <t>交控科技股份有限公司</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24022-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>企业赛</t>
+          <t>高校赛事</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="6">
@@ -2063,27 +2063,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>恶劣场景下的车道线检测挑战赛</t>
+          <t>2026年第八届全国高校计算机能力挑战赛</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>中国矿业大学</t>
+          <t>全国高等学校计算机教育研究会</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>比赛</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t/>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>国家级学会主办，奖项含金量高</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>AI发现·我爱竞赛网</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=lane-detection-challenge</t>
+          <t>https://www.52jingsai.com/article-23886-1.html</t>
         </is>
       </c>
     </row>
@@ -2120,47 +2120,47 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>类脑听觉音频场景分类挑战赛 赛季2</t>
+          <t>2026CCKS系列赛</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t/>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t/>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=DCASE</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
         </is>
       </c>
     </row>
@@ -2177,54 +2177,54 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>智慧交通调度与出行服务</t>
+          <t>2026CCL系列赛</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>交控科技股份有限公司</t>
+          <t/>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>学术顶会论文发表</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t/>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥40,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=its-dispatch</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>高校赛事</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="6">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026年第八届全国高校计算机能力挑战赛</t>
+          <t>CCL25-Eval 打榜赛系列赛</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>全国高等学校计算机教育研究会</t>
+          <t/>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t/>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2254,34 +2254,34 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>奖项及证书</t>
+          <t>¥11,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23886-1.html</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>企业赛</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="6">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>第十三届中国青年创青春大赛</t>
+          <t>野生东北虎个体识别挑战赛</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>共青团中央等</t>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-23888-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
         </is>
       </c>
     </row>
@@ -2348,47 +2348,47 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026CCKS系列赛</t>
+          <t>野生鬣狗个体识别挑战赛</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>自然语言处理、大语言模型、学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/35</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026CCL系列赛</t>
+          <t>野生大熊猫个体识别挑战赛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t/>
+          <t>北京林业大学</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>学术顶会论文发表</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¥40,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/36</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
         </is>
       </c>
     </row>
@@ -2462,47 +2462,47 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CCL25-Eval 打榜赛系列赛</t>
+          <t>企业风险控制与合规管理</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t/>
+          <t>厦门供应链数智创新有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t/>
+          <t>应用</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¥11,000</t>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/19</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>野生东北虎个体识别挑战赛</t>
+          <t>纠错码解码挑战赛</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>合肥工业大学</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildAmurTigerID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>野生鬣狗个体识别挑战赛</t>
+          <t>多模态开放词汇关键词检索挑战赛</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=WildHyenaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
         </is>
       </c>
     </row>
@@ -2633,12 +2633,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>野生大熊猫个体识别挑战赛</t>
+          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>北京林业大学</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=GiantPandaID</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
         </is>
       </c>
     </row>
@@ -2690,27 +2690,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>企业风险控制与合规管理</t>
+          <t>语音质量修复挑战赛 赛季2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>厦门供应链数智创新有限公司</t>
+          <t>声网</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>算法</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Risk-Compliance</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
         </is>
       </c>
     </row>
@@ -2747,12 +2747,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>纠错码解码挑战赛</t>
+          <t>智慧课堂行为识别的目标检测挑战赛</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>合肥工业大学</t>
+          <t>安徽大学、安徽建筑大学</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=ecc-decode-contest</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>多模态开放词汇关键词检索挑战赛</t>
+          <t>船体图像的语义分割挑战赛</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>国家语音及语言信息处理工程研究中心 中国科学技术大学</t>
+          <t>安徽建筑大学、安徽大学</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=MOVKR</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
         </is>
       </c>
     </row>
@@ -2861,27 +2861,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>声纹迷雾复杂场景说话人确认挑战赛</t>
+          <t>智慧家居环境感知与自动化控制</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t>海创汇科技创业发展股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>应用</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SourceSTC</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
         </is>
       </c>
     </row>
@@ -2911,54 +2911,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B50" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>语音质量修复挑战赛 赛季2</t>
+          <t>天池新人实战赛</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>声网</t>
+          <t/>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t/>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=VoiceFixer</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
         </is>
       </c>
     </row>
@@ -2968,54 +2968,54 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B51" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>智慧课堂行为识别的目标检测挑战赛</t>
+          <t>教学系列赛</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>安徽大学、安徽建筑大学</t>
+          <t/>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t/>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t/>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>报名中</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t/>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>科大讯飞开发者大赛</t>
+          <t>阿里云天池</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=SCB-Detection</t>
+          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
         </is>
       </c>
     </row>
@@ -3025,34 +3025,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B52" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>船体图像的语义分割挑战赛</t>
+          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>安徽建筑大学、安徽大学</t>
+          <t>北京科技大学</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3072,64 +3072,64 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=HullSeg-Challenge</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+          <t>企业赛</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026年世界职业院校技能大赛</t>
+          <t>脑PET图像分析和疾病预测练手赛</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>安徽大学</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>待核实</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>国家级奖项</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>AI发现·我爱竞赛网</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.52jingsai.com/article-24019-1.html</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
         </is>
       </c>
     </row>
@@ -3139,34 +3139,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B54" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>智慧家居环境感知与自动化控制</t>
+          <t>基于术语词典干预的机器翻译练手赛</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>海创汇科技创业发展股份有限公司</t>
+          <t>小牛翻译</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>应用</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>¥1万</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=iHome-Auto</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
         </is>
       </c>
     </row>
@@ -3196,34 +3196,34 @@
           <t>企业赛</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr" s="6">
-        <is>
-          <t>中</t>
+      <c r="B55" t="inlineStr" s="7">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AI新睿人才“星探计划”</t>
+          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>烟台睿创微纳技术股份有限公司</t>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>智能算法</t>
+          <t>训练</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>¥90,000</t>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>数据竞赛平台</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1169</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
         </is>
       </c>
     </row>
@@ -3260,47 +3260,47 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>天池新人实战赛</t>
+          <t>分子性质AI预测练手赛</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t/>
+          <t>沈阳药科大学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t/>
+          <t>训练</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t/>
+          <t>¥0万</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/23</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
         </is>
       </c>
     </row>
@@ -3317,47 +3317,47 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>教学系列赛</t>
+          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t/>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t/>
+          <t>算法</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>报名中</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t/>
+          <t>¥1万</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>阿里云天池</t>
+          <t>科大讯飞开发者大赛</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://tianchi.aliyun.com/competition/entrance/24</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>锂离子电池生产参数调控及生产温度预测练手赛</t>
+          <t>用户新增预测练手赛</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-lithium-ion-battery</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-subscriber-addition2025</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>脑PET图像分析和疾病预测练手赛</t>
+          <t>基于带货视频评论的用户洞察练手赛</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>安徽大学</t>
+          <t>科大讯飞股份有限公司</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-pet</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-video-comment-insight</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>基于术语词典干预的机器翻译练手赛</t>
+          <t>电力需求预测练手赛</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>小牛翻译</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-machine-translation</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-electricity-demand</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>基于论文摘要的文本分类与关键词抽取练手赛</t>
+          <t>多模态RAG图文问答练手赛</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-abstract-of-the-paper</t>
+          <t>https://challenge.xfyun.cn/topic/info?type=Train-Multimodal-RAG-QA1</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>分子性质AI预测练手赛</t>
+          <t>少样本语音合成练手赛</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>沈阳药科大学</t>
+          <t>科大讯飞xDatawhale</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3642,354 +3642,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=Train-molecular-properties</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>基于多份材料的信息整合冲突判断与可靠问答挑战赛</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>算法</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>报名中</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>¥1万</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>科大讯飞开发者大赛</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://challenge.xfyun.cn/topic/info?type=FACT-Challenge</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>企业赛</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr" s="7">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>用户新增预测练手赛</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>科大讯飞股份有限公司</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>训练</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
